--- a/tests/tests.xlsx
+++ b/tests/tests.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moto\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moto\team04\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D6CE681-F5A1-4A2C-859C-B7487EDF2062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23FC0BEB-7044-40B0-B3B0-F074E5B84B93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="テスト記録" sheetId="1" r:id="rId1"/>
@@ -183,7 +183,7 @@
     <t>改善案や気づいたことを書く。</t>
   </si>
   <si>
-    <t>test 01-3</t>
+    <t>test 02-1</t>
     <phoneticPr fontId="6"/>
   </si>
 </sst>
@@ -294,14 +294,14 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -562,20 +562,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="20" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
@@ -734,7 +734,7 @@
       <c r="L9" s="6"/>
     </row>
     <row r="10" spans="1:12" ht="42.65" customHeight="1">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="9" t="s">
         <v>49</v>
       </c>
       <c r="B10" s="6"/>
@@ -3458,14 +3458,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
     </row>
     <row r="3" spans="1:6" ht="22.65" customHeight="1">
       <c r="A3" s="8" t="s">

--- a/tests/tests.xlsx
+++ b/tests/tests.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moto\team04\tests\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1f3453c015a41521/デスクトップ/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23FC0BEB-7044-40B0-B3B0-F074E5B84B93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD370010-200F-4853-A1FE-741A27A94439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="テスト記録" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="80">
   <si>
     <t>ゲーム動作テスト記録</t>
   </si>
@@ -96,48 +96,15 @@
     <t>01-1</t>
   </si>
   <si>
-    <t>番号順にクリック</t>
-  </si>
-  <si>
-    <t>阿萬裕久</t>
-  </si>
-  <si>
-    <t>ゲームを開始し、アイコンが表示されていること</t>
-  </si>
-  <si>
-    <t>表示されるアイコンを番号順にクリックする。</t>
-  </si>
-  <si>
-    <t>クリックしたアイコンが消え、画面に「クリア」と残り時間が表示される。</t>
-  </si>
-  <si>
     <t>期待される結果どおりとなった。</t>
   </si>
   <si>
     <t>未確認</t>
   </si>
   <si>
-    <t>うまくクリックできた時に反応があると、より面白いと感じた。</t>
-  </si>
-  <si>
     <t>01-2</t>
   </si>
   <si>
-    <t>逆順にクリック</t>
-  </si>
-  <si>
-    <t>表示されるアイコンを番号とは逆順にクリックする。</t>
-  </si>
-  <si>
-    <t>画面に「Miss」と表示され、残り時間が減る。アイコンはそのまま表示され続ける。</t>
-  </si>
-  <si>
-    <t>「Miss」は表示されたが、残り時間が減らなかった。</t>
-  </si>
-  <si>
-    <t>ミス時に残り時間が減少しない。</t>
-  </si>
-  <si>
     <t>テスト記録の使い方</t>
   </si>
   <si>
@@ -183,7 +150,452 @@
     <t>改善案や気づいたことを書く。</t>
   </si>
   <si>
-    <t>test 02-1</t>
+    <t>梁瀬結月</t>
+    <rPh sb="0" eb="4">
+      <t>ヤナセユヅキ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>タイトル画面のゲーム開始をクリック</t>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カイシ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>タイトル画面で</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Enter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>キーを押すと、ゲームが開始される</t>
+    </r>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>カイシ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <r>
+      <t>processing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>を実行できて、タイトル画面にいること。</t>
+    </r>
+    <rPh sb="11" eb="13">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <r>
+      <t>processing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>を実行できて、タイトル画面にいること。</t>
+    </r>
+  </si>
+  <si>
+    <t>タイトル画面で、Enterキーを押す</t>
+    <rPh sb="16" eb="17">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>期待される結果どおりとなった。</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>01-3</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>ゲーム終了をクリックすると、ゲームを終了する</t>
+    <rPh sb="3" eb="5">
+      <t>シュウリョウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>シュウリョウ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>ゲーム開始をクリックすると、ゲームが開始される。</t>
+    <rPh sb="3" eb="5">
+      <t>カイシ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>カイシ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>タイトル画面のゲーム終了をクリック</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>ゲームが終了される</t>
+    <rPh sb="4" eb="6">
+      <t>シュウリョウ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>ゲームが開始される</t>
+    <rPh sb="4" eb="6">
+      <t>カイシ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>01-4</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>オプションをクリックすると、モードが選択できる。</t>
+    <rPh sb="18" eb="20">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>01-5</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>01-6</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <r>
+      <t>processing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>を実行できて、タイトル画面にいること。</t>
+    </r>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>オプションが表示され、NOMALかHARDの2つが選択できる。</t>
+    <rPh sb="6" eb="8">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>01-7</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>01-8</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>01-9</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>タイトル画面のオプションをクリックし、モードを選ぶ。</t>
+    <rPh sb="23" eb="24">
+      <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>タイトル画面のオプションをクリックし、操作説明をクリックする</t>
+    <rPh sb="19" eb="21">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <r>
+      <t>NOMAL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>モード、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>HARD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>モードの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>つの説明が表示される。</t>
+    </r>
+  </si>
+  <si>
+    <t>オプションの操作説明ボタンをクリックすると、操作の説明が表示される。</t>
+    <rPh sb="6" eb="8">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>オプションのゲーム説明ボタンをクリックすると、NORMALモード、HARDモードの2つの説明が見れる</t>
+    <rPh sb="9" eb="11">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>タイトル画面のオプションをクリックし、ゲーム説明をクリックする</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>オプションをクリックすると、操作説明が表示される</t>
+    <rPh sb="14" eb="16">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>オプション画面からタイトル画面に戻れる</t>
+    <rPh sb="5" eb="7">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>ゲーム説明をクリックした後、「戻る」をクリックするとオプション画面に戻れる。</t>
+    <rPh sb="3" eb="5">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>モド</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>操作説明をクリックした後、「戻る」をクリックするとオプション画面に戻れる</t>
+    <rPh sb="0" eb="4">
+      <t>ソウサセツメイ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>モド</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>タイトル画面のオプションをクリックし、オプション画面にいること。</t>
+  </si>
+  <si>
+    <t>タイトル画面のオプションをクリックし、オプション画面にいること。</t>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>操作説明画面にいること</t>
+    <rPh sb="0" eb="4">
+      <t>ソウサセツメイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>ゲーム説明画面にいること</t>
+    <rPh sb="3" eb="5">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>オプション画面にいること</t>
+    <rPh sb="5" eb="7">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>操作説明画面の下の「戻る」をクリック</t>
+    <rPh sb="0" eb="4">
+      <t>ソウサセツメイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>シタ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>ゲーム説明画面の下の「戻る」をクリック</t>
+    <rPh sb="5" eb="7">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>オプション画面の「タイトルへ戻る」をクリック</t>
+    <rPh sb="5" eb="7">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>オプション画面に戻る</t>
+    <rPh sb="5" eb="7">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>タイトル画面に戻る</t>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>モド</t>
+    </rPh>
     <phoneticPr fontId="6"/>
   </si>
 </sst>
@@ -194,7 +606,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -227,6 +639,29 @@
     </font>
     <font>
       <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
@@ -268,7 +703,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -294,14 +729,26 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -545,7 +992,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L200"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -561,21 +1008,21 @@
     <col min="12" max="12" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="20" customHeight="1">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:12" ht="19.95" customHeight="1">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
@@ -597,18 +1044,18 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="15.5">
+    <row r="4" spans="1:12" ht="15.6">
       <c r="A4" s="2">
         <f>COUNTA(A8:A200)</f>
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B4" s="2">
         <f>COUNTIF(J8:J200,"OK")</f>
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C4" s="2">
         <f>COUNTIF(J8:J200,"不具合あり")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" s="2">
         <f>COUNTIF(J8:J200,"未実施")</f>
@@ -616,11 +1063,10 @@
       </c>
       <c r="E4" s="3">
         <f>IF(A4=0,0,B4/A4)</f>
-        <v>0.33333333333333331</v>
+        <v>1.1111111111111112</v>
       </c>
       <c r="F4" s="4">
-        <f>MAX(D8:D200)</f>
-        <v>45847.475694444445</v>
+        <v>45857.513194444444</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="22.65" customHeight="1">
@@ -661,179 +1107,299 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="42.65" customHeight="1">
+    <row r="8" spans="1:12" ht="42.6" customHeight="1">
       <c r="A8" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>20</v>
+      <c r="B8" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="D8" s="7">
-        <v>45847.472916666666</v>
+        <v>46222.513194444444</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>25</v>
+        <v>41</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>44</v>
       </c>
       <c r="I8" s="6"/>
       <c r="J8" s="6" t="s">
         <v>2</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L8" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="42.65" customHeight="1">
+        <v>21</v>
+      </c>
+      <c r="L8" s="6"/>
+    </row>
+    <row r="9" spans="1:12" ht="42.6" customHeight="1">
       <c r="A9" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>29</v>
+        <v>22</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>40</v>
       </c>
       <c r="C9" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="7">
+        <v>46222.513194444444</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="I9" s="6"/>
+      <c r="J9" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="K9" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="7">
-        <v>45847.475694444445</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="K9" s="6" t="s">
-        <v>26</v>
-      </c>
       <c r="L9" s="6"/>
     </row>
-    <row r="10" spans="1:12" ht="42.65" customHeight="1">
-      <c r="A10" s="9" t="s">
+    <row r="10" spans="1:12" ht="42.6" customHeight="1">
+      <c r="A10" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="7">
+        <v>46222.513194444444</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="G10" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
+      <c r="H10" s="13" t="s">
+        <v>44</v>
+      </c>
       <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
+      <c r="J10" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="K10" s="6"/>
       <c r="L10" s="6"/>
     </row>
-    <row r="11" spans="1:12" ht="42.65" customHeight="1">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
+    <row r="11" spans="1:12" ht="42.6" customHeight="1">
+      <c r="A11" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="7">
+        <v>46222.513194444444</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="H11" s="13" t="s">
+        <v>44</v>
+      </c>
       <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
+      <c r="J11" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="K11" s="6"/>
       <c r="L11" s="6"/>
     </row>
-    <row r="12" spans="1:12" ht="42.65" customHeight="1">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
+    <row r="12" spans="1:12" ht="42.6" customHeight="1">
+      <c r="A12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="7">
+        <v>45857.513194444444</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>44</v>
+      </c>
       <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
+      <c r="J12" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="K12" s="6"/>
       <c r="L12" s="6"/>
     </row>
-    <row r="13" spans="1:12" ht="42.65" customHeight="1">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
+    <row r="13" spans="1:12" ht="42.6" customHeight="1">
+      <c r="A13" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" s="7">
+        <v>46223</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="H13" s="13" t="s">
+        <v>44</v>
+      </c>
       <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
+      <c r="J13" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="K13" s="6"/>
       <c r="L13" s="6"/>
     </row>
-    <row r="14" spans="1:12" ht="42.65" customHeight="1">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
+    <row r="14" spans="1:12" ht="42.6" customHeight="1">
+      <c r="A14" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="7">
+        <v>46223</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>20</v>
+      </c>
       <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
+      <c r="J14" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="K14" s="6"/>
       <c r="L14" s="6"/>
     </row>
-    <row r="15" spans="1:12" ht="42.65" customHeight="1">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
+    <row r="15" spans="1:12" ht="42.6" customHeight="1">
+      <c r="A15" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" s="7">
+        <v>46223</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>20</v>
+      </c>
       <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
+      <c r="J15" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="K15" s="6"/>
       <c r="L15" s="6"/>
     </row>
-    <row r="16" spans="1:12" ht="42.65" customHeight="1">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
+    <row r="16" spans="1:12" ht="42.6" customHeight="1">
+      <c r="A16" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="7">
+        <v>46223</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>20</v>
+      </c>
       <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
+      <c r="J16" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="K16" s="6"/>
       <c r="L16" s="6"/>
     </row>
-    <row r="17" spans="1:12" ht="42.65" customHeight="1">
+    <row r="17" spans="1:12" ht="42.6" customHeight="1">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -841,13 +1407,15 @@
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
+      <c r="H17" s="13"/>
       <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
+      <c r="J17" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="K17" s="6"/>
       <c r="L17" s="6"/>
     </row>
-    <row r="18" spans="1:12" ht="42.65" customHeight="1">
+    <row r="18" spans="1:12" ht="42.6" customHeight="1">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -861,7 +1429,7 @@
       <c r="K18" s="6"/>
       <c r="L18" s="6"/>
     </row>
-    <row r="19" spans="1:12" ht="42.65" customHeight="1">
+    <row r="19" spans="1:12" ht="42.6" customHeight="1">
       <c r="A19" s="6"/>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
@@ -875,7 +1443,7 @@
       <c r="K19" s="6"/>
       <c r="L19" s="6"/>
     </row>
-    <row r="20" spans="1:12" ht="42.65" customHeight="1">
+    <row r="20" spans="1:12" ht="42.6" customHeight="1">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -889,7 +1457,7 @@
       <c r="K20" s="6"/>
       <c r="L20" s="6"/>
     </row>
-    <row r="21" spans="1:12" ht="42.65" customHeight="1">
+    <row r="21" spans="1:12" ht="42.6" customHeight="1">
       <c r="A21" s="6"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -903,7 +1471,7 @@
       <c r="K21" s="6"/>
       <c r="L21" s="6"/>
     </row>
-    <row r="22" spans="1:12" ht="42.65" customHeight="1">
+    <row r="22" spans="1:12" ht="42.6" customHeight="1">
       <c r="A22" s="6"/>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
@@ -917,7 +1485,7 @@
       <c r="K22" s="6"/>
       <c r="L22" s="6"/>
     </row>
-    <row r="23" spans="1:12" ht="42.65" customHeight="1">
+    <row r="23" spans="1:12" ht="42.6" customHeight="1">
       <c r="A23" s="6"/>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
@@ -931,7 +1499,7 @@
       <c r="K23" s="6"/>
       <c r="L23" s="6"/>
     </row>
-    <row r="24" spans="1:12" ht="42.65" customHeight="1">
+    <row r="24" spans="1:12" ht="42.6" customHeight="1">
       <c r="A24" s="6"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -945,7 +1513,7 @@
       <c r="K24" s="6"/>
       <c r="L24" s="6"/>
     </row>
-    <row r="25" spans="1:12" ht="42.65" customHeight="1">
+    <row r="25" spans="1:12" ht="42.6" customHeight="1">
       <c r="A25" s="6"/>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
@@ -959,7 +1527,7 @@
       <c r="K25" s="6"/>
       <c r="L25" s="6"/>
     </row>
-    <row r="26" spans="1:12" ht="42.65" customHeight="1">
+    <row r="26" spans="1:12" ht="42.6" customHeight="1">
       <c r="A26" s="6"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
@@ -973,7 +1541,7 @@
       <c r="K26" s="6"/>
       <c r="L26" s="6"/>
     </row>
-    <row r="27" spans="1:12" ht="42.65" customHeight="1">
+    <row r="27" spans="1:12" ht="42.6" customHeight="1">
       <c r="A27" s="6"/>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
@@ -987,7 +1555,7 @@
       <c r="K27" s="6"/>
       <c r="L27" s="6"/>
     </row>
-    <row r="28" spans="1:12" ht="42.65" customHeight="1">
+    <row r="28" spans="1:12" ht="42.6" customHeight="1">
       <c r="A28" s="6"/>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -1001,7 +1569,7 @@
       <c r="K28" s="6"/>
       <c r="L28" s="6"/>
     </row>
-    <row r="29" spans="1:12" ht="42.65" customHeight="1">
+    <row r="29" spans="1:12" ht="42.6" customHeight="1">
       <c r="A29" s="6"/>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
@@ -1015,7 +1583,7 @@
       <c r="K29" s="6"/>
       <c r="L29" s="6"/>
     </row>
-    <row r="30" spans="1:12" ht="42.65" customHeight="1">
+    <row r="30" spans="1:12" ht="42.6" customHeight="1">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -1029,7 +1597,7 @@
       <c r="K30" s="6"/>
       <c r="L30" s="6"/>
     </row>
-    <row r="31" spans="1:12" ht="42.65" customHeight="1">
+    <row r="31" spans="1:12" ht="42.6" customHeight="1">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -1043,7 +1611,7 @@
       <c r="K31" s="6"/>
       <c r="L31" s="6"/>
     </row>
-    <row r="32" spans="1:12" ht="42.65" customHeight="1">
+    <row r="32" spans="1:12" ht="42.6" customHeight="1">
       <c r="A32" s="6"/>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
@@ -1057,7 +1625,7 @@
       <c r="K32" s="6"/>
       <c r="L32" s="6"/>
     </row>
-    <row r="33" spans="1:12" ht="42.65" customHeight="1">
+    <row r="33" spans="1:12" ht="42.6" customHeight="1">
       <c r="A33" s="6"/>
       <c r="B33" s="6"/>
       <c r="C33" s="6"/>
@@ -1071,7 +1639,7 @@
       <c r="K33" s="6"/>
       <c r="L33" s="6"/>
     </row>
-    <row r="34" spans="1:12" ht="42.65" customHeight="1">
+    <row r="34" spans="1:12" ht="42.6" customHeight="1">
       <c r="A34" s="6"/>
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
@@ -1085,7 +1653,7 @@
       <c r="K34" s="6"/>
       <c r="L34" s="6"/>
     </row>
-    <row r="35" spans="1:12" ht="42.65" customHeight="1">
+    <row r="35" spans="1:12" ht="42.6" customHeight="1">
       <c r="A35" s="6"/>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
@@ -1099,7 +1667,7 @@
       <c r="K35" s="6"/>
       <c r="L35" s="6"/>
     </row>
-    <row r="36" spans="1:12" ht="42.65" customHeight="1">
+    <row r="36" spans="1:12" ht="42.6" customHeight="1">
       <c r="A36" s="6"/>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -1113,7 +1681,7 @@
       <c r="K36" s="6"/>
       <c r="L36" s="6"/>
     </row>
-    <row r="37" spans="1:12" ht="42.65" customHeight="1">
+    <row r="37" spans="1:12" ht="42.6" customHeight="1">
       <c r="A37" s="6"/>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -1127,7 +1695,7 @@
       <c r="K37" s="6"/>
       <c r="L37" s="6"/>
     </row>
-    <row r="38" spans="1:12" ht="42.65" customHeight="1">
+    <row r="38" spans="1:12" ht="42.6" customHeight="1">
       <c r="A38" s="6"/>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
@@ -1141,7 +1709,7 @@
       <c r="K38" s="6"/>
       <c r="L38" s="6"/>
     </row>
-    <row r="39" spans="1:12" ht="42.65" customHeight="1">
+    <row r="39" spans="1:12" ht="42.6" customHeight="1">
       <c r="A39" s="6"/>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
@@ -1155,7 +1723,7 @@
       <c r="K39" s="6"/>
       <c r="L39" s="6"/>
     </row>
-    <row r="40" spans="1:12" ht="42.65" customHeight="1">
+    <row r="40" spans="1:12" ht="42.6" customHeight="1">
       <c r="A40" s="6"/>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
@@ -1169,7 +1737,7 @@
       <c r="K40" s="6"/>
       <c r="L40" s="6"/>
     </row>
-    <row r="41" spans="1:12" ht="42.65" customHeight="1">
+    <row r="41" spans="1:12" ht="42.6" customHeight="1">
       <c r="A41" s="6"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -1183,7 +1751,7 @@
       <c r="K41" s="6"/>
       <c r="L41" s="6"/>
     </row>
-    <row r="42" spans="1:12" ht="42.65" customHeight="1">
+    <row r="42" spans="1:12" ht="42.6" customHeight="1">
       <c r="A42" s="6"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
@@ -1197,7 +1765,7 @@
       <c r="K42" s="6"/>
       <c r="L42" s="6"/>
     </row>
-    <row r="43" spans="1:12" ht="42.65" customHeight="1">
+    <row r="43" spans="1:12" ht="42.6" customHeight="1">
       <c r="A43" s="6"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
@@ -1211,7 +1779,7 @@
       <c r="K43" s="6"/>
       <c r="L43" s="6"/>
     </row>
-    <row r="44" spans="1:12" ht="42.65" customHeight="1">
+    <row r="44" spans="1:12" ht="42.6" customHeight="1">
       <c r="A44" s="6"/>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
@@ -1225,7 +1793,7 @@
       <c r="K44" s="6"/>
       <c r="L44" s="6"/>
     </row>
-    <row r="45" spans="1:12" ht="42.65" customHeight="1">
+    <row r="45" spans="1:12" ht="42.6" customHeight="1">
       <c r="A45" s="6"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
@@ -1239,7 +1807,7 @@
       <c r="K45" s="6"/>
       <c r="L45" s="6"/>
     </row>
-    <row r="46" spans="1:12" ht="42.65" customHeight="1">
+    <row r="46" spans="1:12" ht="42.6" customHeight="1">
       <c r="A46" s="6"/>
       <c r="B46" s="6"/>
       <c r="C46" s="6"/>
@@ -1253,7 +1821,7 @@
       <c r="K46" s="6"/>
       <c r="L46" s="6"/>
     </row>
-    <row r="47" spans="1:12" ht="42.65" customHeight="1">
+    <row r="47" spans="1:12" ht="42.6" customHeight="1">
       <c r="A47" s="6"/>
       <c r="B47" s="6"/>
       <c r="C47" s="6"/>
@@ -1267,7 +1835,7 @@
       <c r="K47" s="6"/>
       <c r="L47" s="6"/>
     </row>
-    <row r="48" spans="1:12" ht="42.65" customHeight="1">
+    <row r="48" spans="1:12" ht="42.6" customHeight="1">
       <c r="A48" s="6"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
@@ -1281,7 +1849,7 @@
       <c r="K48" s="6"/>
       <c r="L48" s="6"/>
     </row>
-    <row r="49" spans="1:12" ht="42.65" customHeight="1">
+    <row r="49" spans="1:12" ht="42.6" customHeight="1">
       <c r="A49" s="6"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -1295,7 +1863,7 @@
       <c r="K49" s="6"/>
       <c r="L49" s="6"/>
     </row>
-    <row r="50" spans="1:12" ht="42.65" customHeight="1">
+    <row r="50" spans="1:12" ht="42.6" customHeight="1">
       <c r="A50" s="6"/>
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
@@ -1309,7 +1877,7 @@
       <c r="K50" s="6"/>
       <c r="L50" s="6"/>
     </row>
-    <row r="51" spans="1:12" ht="42.65" customHeight="1">
+    <row r="51" spans="1:12" ht="42.6" customHeight="1">
       <c r="A51" s="6"/>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
@@ -1323,7 +1891,7 @@
       <c r="K51" s="6"/>
       <c r="L51" s="6"/>
     </row>
-    <row r="52" spans="1:12" ht="42.65" customHeight="1">
+    <row r="52" spans="1:12" ht="42.6" customHeight="1">
       <c r="A52" s="6"/>
       <c r="B52" s="6"/>
       <c r="C52" s="6"/>
@@ -1337,7 +1905,7 @@
       <c r="K52" s="6"/>
       <c r="L52" s="6"/>
     </row>
-    <row r="53" spans="1:12" ht="42.65" customHeight="1">
+    <row r="53" spans="1:12" ht="42.6" customHeight="1">
       <c r="A53" s="6"/>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
@@ -1351,7 +1919,7 @@
       <c r="K53" s="6"/>
       <c r="L53" s="6"/>
     </row>
-    <row r="54" spans="1:12" ht="42.65" customHeight="1">
+    <row r="54" spans="1:12" ht="42.6" customHeight="1">
       <c r="A54" s="6"/>
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
@@ -1365,7 +1933,7 @@
       <c r="K54" s="6"/>
       <c r="L54" s="6"/>
     </row>
-    <row r="55" spans="1:12" ht="42.65" customHeight="1">
+    <row r="55" spans="1:12" ht="42.6" customHeight="1">
       <c r="A55" s="6"/>
       <c r="B55" s="6"/>
       <c r="C55" s="6"/>
@@ -1379,7 +1947,7 @@
       <c r="K55" s="6"/>
       <c r="L55" s="6"/>
     </row>
-    <row r="56" spans="1:12" ht="42.65" customHeight="1">
+    <row r="56" spans="1:12" ht="42.6" customHeight="1">
       <c r="A56" s="6"/>
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
@@ -1393,7 +1961,7 @@
       <c r="K56" s="6"/>
       <c r="L56" s="6"/>
     </row>
-    <row r="57" spans="1:12" ht="42.65" customHeight="1">
+    <row r="57" spans="1:12" ht="42.6" customHeight="1">
       <c r="A57" s="6"/>
       <c r="B57" s="6"/>
       <c r="C57" s="6"/>
@@ -1407,7 +1975,7 @@
       <c r="K57" s="6"/>
       <c r="L57" s="6"/>
     </row>
-    <row r="58" spans="1:12" ht="42.65" customHeight="1">
+    <row r="58" spans="1:12" ht="42.6" customHeight="1">
       <c r="A58" s="6"/>
       <c r="B58" s="6"/>
       <c r="C58" s="6"/>
@@ -1421,7 +1989,7 @@
       <c r="K58" s="6"/>
       <c r="L58" s="6"/>
     </row>
-    <row r="59" spans="1:12" ht="42.65" customHeight="1">
+    <row r="59" spans="1:12" ht="42.6" customHeight="1">
       <c r="A59" s="6"/>
       <c r="B59" s="6"/>
       <c r="C59" s="6"/>
@@ -1435,7 +2003,7 @@
       <c r="K59" s="6"/>
       <c r="L59" s="6"/>
     </row>
-    <row r="60" spans="1:12" ht="42.65" customHeight="1">
+    <row r="60" spans="1:12" ht="42.6" customHeight="1">
       <c r="A60" s="6"/>
       <c r="B60" s="6"/>
       <c r="C60" s="6"/>
@@ -1449,7 +2017,7 @@
       <c r="K60" s="6"/>
       <c r="L60" s="6"/>
     </row>
-    <row r="61" spans="1:12" ht="42.65" customHeight="1">
+    <row r="61" spans="1:12" ht="42.6" customHeight="1">
       <c r="A61" s="6"/>
       <c r="B61" s="6"/>
       <c r="C61" s="6"/>
@@ -1463,7 +2031,7 @@
       <c r="K61" s="6"/>
       <c r="L61" s="6"/>
     </row>
-    <row r="62" spans="1:12" ht="42.65" customHeight="1">
+    <row r="62" spans="1:12" ht="42.6" customHeight="1">
       <c r="A62" s="6"/>
       <c r="B62" s="6"/>
       <c r="C62" s="6"/>
@@ -1477,7 +2045,7 @@
       <c r="K62" s="6"/>
       <c r="L62" s="6"/>
     </row>
-    <row r="63" spans="1:12" ht="42.65" customHeight="1">
+    <row r="63" spans="1:12" ht="42.6" customHeight="1">
       <c r="A63" s="6"/>
       <c r="B63" s="6"/>
       <c r="C63" s="6"/>
@@ -1491,7 +2059,7 @@
       <c r="K63" s="6"/>
       <c r="L63" s="6"/>
     </row>
-    <row r="64" spans="1:12" ht="42.65" customHeight="1">
+    <row r="64" spans="1:12" ht="42.6" customHeight="1">
       <c r="A64" s="6"/>
       <c r="B64" s="6"/>
       <c r="C64" s="6"/>
@@ -1505,7 +2073,7 @@
       <c r="K64" s="6"/>
       <c r="L64" s="6"/>
     </row>
-    <row r="65" spans="1:12" ht="42.65" customHeight="1">
+    <row r="65" spans="1:12" ht="42.6" customHeight="1">
       <c r="A65" s="6"/>
       <c r="B65" s="6"/>
       <c r="C65" s="6"/>
@@ -1519,7 +2087,7 @@
       <c r="K65" s="6"/>
       <c r="L65" s="6"/>
     </row>
-    <row r="66" spans="1:12" ht="42.65" customHeight="1">
+    <row r="66" spans="1:12" ht="42.6" customHeight="1">
       <c r="A66" s="6"/>
       <c r="B66" s="6"/>
       <c r="C66" s="6"/>
@@ -1533,7 +2101,7 @@
       <c r="K66" s="6"/>
       <c r="L66" s="6"/>
     </row>
-    <row r="67" spans="1:12" ht="42.65" customHeight="1">
+    <row r="67" spans="1:12" ht="42.6" customHeight="1">
       <c r="A67" s="6"/>
       <c r="B67" s="6"/>
       <c r="C67" s="6"/>
@@ -1547,7 +2115,7 @@
       <c r="K67" s="6"/>
       <c r="L67" s="6"/>
     </row>
-    <row r="68" spans="1:12" ht="42.65" customHeight="1">
+    <row r="68" spans="1:12" ht="42.6" customHeight="1">
       <c r="A68" s="6"/>
       <c r="B68" s="6"/>
       <c r="C68" s="6"/>
@@ -1561,7 +2129,7 @@
       <c r="K68" s="6"/>
       <c r="L68" s="6"/>
     </row>
-    <row r="69" spans="1:12" ht="42.65" customHeight="1">
+    <row r="69" spans="1:12" ht="42.6" customHeight="1">
       <c r="A69" s="6"/>
       <c r="B69" s="6"/>
       <c r="C69" s="6"/>
@@ -1575,7 +2143,7 @@
       <c r="K69" s="6"/>
       <c r="L69" s="6"/>
     </row>
-    <row r="70" spans="1:12" ht="42.65" customHeight="1">
+    <row r="70" spans="1:12" ht="42.6" customHeight="1">
       <c r="A70" s="6"/>
       <c r="B70" s="6"/>
       <c r="C70" s="6"/>
@@ -1589,7 +2157,7 @@
       <c r="K70" s="6"/>
       <c r="L70" s="6"/>
     </row>
-    <row r="71" spans="1:12" ht="42.65" customHeight="1">
+    <row r="71" spans="1:12" ht="42.6" customHeight="1">
       <c r="A71" s="6"/>
       <c r="B71" s="6"/>
       <c r="C71" s="6"/>
@@ -1603,7 +2171,7 @@
       <c r="K71" s="6"/>
       <c r="L71" s="6"/>
     </row>
-    <row r="72" spans="1:12" ht="42.65" customHeight="1">
+    <row r="72" spans="1:12" ht="42.6" customHeight="1">
       <c r="A72" s="6"/>
       <c r="B72" s="6"/>
       <c r="C72" s="6"/>
@@ -1617,7 +2185,7 @@
       <c r="K72" s="6"/>
       <c r="L72" s="6"/>
     </row>
-    <row r="73" spans="1:12" ht="42.65" customHeight="1">
+    <row r="73" spans="1:12" ht="42.6" customHeight="1">
       <c r="A73" s="6"/>
       <c r="B73" s="6"/>
       <c r="C73" s="6"/>
@@ -1631,7 +2199,7 @@
       <c r="K73" s="6"/>
       <c r="L73" s="6"/>
     </row>
-    <row r="74" spans="1:12" ht="42.65" customHeight="1">
+    <row r="74" spans="1:12" ht="42.6" customHeight="1">
       <c r="A74" s="6"/>
       <c r="B74" s="6"/>
       <c r="C74" s="6"/>
@@ -1645,7 +2213,7 @@
       <c r="K74" s="6"/>
       <c r="L74" s="6"/>
     </row>
-    <row r="75" spans="1:12" ht="42.65" customHeight="1">
+    <row r="75" spans="1:12" ht="42.6" customHeight="1">
       <c r="A75" s="6"/>
       <c r="B75" s="6"/>
       <c r="C75" s="6"/>
@@ -1659,7 +2227,7 @@
       <c r="K75" s="6"/>
       <c r="L75" s="6"/>
     </row>
-    <row r="76" spans="1:12" ht="42.65" customHeight="1">
+    <row r="76" spans="1:12" ht="42.6" customHeight="1">
       <c r="A76" s="6"/>
       <c r="B76" s="6"/>
       <c r="C76" s="6"/>
@@ -1673,7 +2241,7 @@
       <c r="K76" s="6"/>
       <c r="L76" s="6"/>
     </row>
-    <row r="77" spans="1:12" ht="42.65" customHeight="1">
+    <row r="77" spans="1:12" ht="42.6" customHeight="1">
       <c r="A77" s="6"/>
       <c r="B77" s="6"/>
       <c r="C77" s="6"/>
@@ -1687,7 +2255,7 @@
       <c r="K77" s="6"/>
       <c r="L77" s="6"/>
     </row>
-    <row r="78" spans="1:12" ht="42.65" customHeight="1">
+    <row r="78" spans="1:12" ht="42.6" customHeight="1">
       <c r="A78" s="6"/>
       <c r="B78" s="6"/>
       <c r="C78" s="6"/>
@@ -1701,7 +2269,7 @@
       <c r="K78" s="6"/>
       <c r="L78" s="6"/>
     </row>
-    <row r="79" spans="1:12" ht="42.65" customHeight="1">
+    <row r="79" spans="1:12" ht="42.6" customHeight="1">
       <c r="A79" s="6"/>
       <c r="B79" s="6"/>
       <c r="C79" s="6"/>
@@ -1715,7 +2283,7 @@
       <c r="K79" s="6"/>
       <c r="L79" s="6"/>
     </row>
-    <row r="80" spans="1:12" ht="42.65" customHeight="1">
+    <row r="80" spans="1:12" ht="42.6" customHeight="1">
       <c r="A80" s="6"/>
       <c r="B80" s="6"/>
       <c r="C80" s="6"/>
@@ -1729,7 +2297,7 @@
       <c r="K80" s="6"/>
       <c r="L80" s="6"/>
     </row>
-    <row r="81" spans="1:12" ht="42.65" customHeight="1">
+    <row r="81" spans="1:12" ht="42.6" customHeight="1">
       <c r="A81" s="6"/>
       <c r="B81" s="6"/>
       <c r="C81" s="6"/>
@@ -1743,7 +2311,7 @@
       <c r="K81" s="6"/>
       <c r="L81" s="6"/>
     </row>
-    <row r="82" spans="1:12" ht="42.65" customHeight="1">
+    <row r="82" spans="1:12" ht="42.6" customHeight="1">
       <c r="A82" s="6"/>
       <c r="B82" s="6"/>
       <c r="C82" s="6"/>
@@ -1757,7 +2325,7 @@
       <c r="K82" s="6"/>
       <c r="L82" s="6"/>
     </row>
-    <row r="83" spans="1:12" ht="42.65" customHeight="1">
+    <row r="83" spans="1:12" ht="42.6" customHeight="1">
       <c r="A83" s="6"/>
       <c r="B83" s="6"/>
       <c r="C83" s="6"/>
@@ -1771,7 +2339,7 @@
       <c r="K83" s="6"/>
       <c r="L83" s="6"/>
     </row>
-    <row r="84" spans="1:12" ht="42.65" customHeight="1">
+    <row r="84" spans="1:12" ht="42.6" customHeight="1">
       <c r="A84" s="6"/>
       <c r="B84" s="6"/>
       <c r="C84" s="6"/>
@@ -1785,7 +2353,7 @@
       <c r="K84" s="6"/>
       <c r="L84" s="6"/>
     </row>
-    <row r="85" spans="1:12" ht="42.65" customHeight="1">
+    <row r="85" spans="1:12" ht="42.6" customHeight="1">
       <c r="A85" s="6"/>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
@@ -1799,7 +2367,7 @@
       <c r="K85" s="6"/>
       <c r="L85" s="6"/>
     </row>
-    <row r="86" spans="1:12" ht="42.65" customHeight="1">
+    <row r="86" spans="1:12" ht="42.6" customHeight="1">
       <c r="A86" s="6"/>
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
@@ -1813,7 +2381,7 @@
       <c r="K86" s="6"/>
       <c r="L86" s="6"/>
     </row>
-    <row r="87" spans="1:12" ht="42.65" customHeight="1">
+    <row r="87" spans="1:12" ht="42.6" customHeight="1">
       <c r="A87" s="6"/>
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
@@ -1827,7 +2395,7 @@
       <c r="K87" s="6"/>
       <c r="L87" s="6"/>
     </row>
-    <row r="88" spans="1:12" ht="42.65" customHeight="1">
+    <row r="88" spans="1:12" ht="42.6" customHeight="1">
       <c r="A88" s="6"/>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
@@ -1841,7 +2409,7 @@
       <c r="K88" s="6"/>
       <c r="L88" s="6"/>
     </row>
-    <row r="89" spans="1:12" ht="42.65" customHeight="1">
+    <row r="89" spans="1:12" ht="42.6" customHeight="1">
       <c r="A89" s="6"/>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
@@ -1855,7 +2423,7 @@
       <c r="K89" s="6"/>
       <c r="L89" s="6"/>
     </row>
-    <row r="90" spans="1:12" ht="42.65" customHeight="1">
+    <row r="90" spans="1:12" ht="42.6" customHeight="1">
       <c r="A90" s="6"/>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
@@ -1869,7 +2437,7 @@
       <c r="K90" s="6"/>
       <c r="L90" s="6"/>
     </row>
-    <row r="91" spans="1:12" ht="42.65" customHeight="1">
+    <row r="91" spans="1:12" ht="42.6" customHeight="1">
       <c r="A91" s="6"/>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
@@ -1883,7 +2451,7 @@
       <c r="K91" s="6"/>
       <c r="L91" s="6"/>
     </row>
-    <row r="92" spans="1:12" ht="42.65" customHeight="1">
+    <row r="92" spans="1:12" ht="42.6" customHeight="1">
       <c r="A92" s="6"/>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
@@ -1897,7 +2465,7 @@
       <c r="K92" s="6"/>
       <c r="L92" s="6"/>
     </row>
-    <row r="93" spans="1:12" ht="42.65" customHeight="1">
+    <row r="93" spans="1:12" ht="42.6" customHeight="1">
       <c r="A93" s="6"/>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -1911,7 +2479,7 @@
       <c r="K93" s="6"/>
       <c r="L93" s="6"/>
     </row>
-    <row r="94" spans="1:12" ht="42.65" customHeight="1">
+    <row r="94" spans="1:12" ht="42.6" customHeight="1">
       <c r="A94" s="6"/>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -1925,7 +2493,7 @@
       <c r="K94" s="6"/>
       <c r="L94" s="6"/>
     </row>
-    <row r="95" spans="1:12" ht="42.65" customHeight="1">
+    <row r="95" spans="1:12" ht="42.6" customHeight="1">
       <c r="A95" s="6"/>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -1939,7 +2507,7 @@
       <c r="K95" s="6"/>
       <c r="L95" s="6"/>
     </row>
-    <row r="96" spans="1:12" ht="42.65" customHeight="1">
+    <row r="96" spans="1:12" ht="42.6" customHeight="1">
       <c r="A96" s="6"/>
       <c r="B96" s="6"/>
       <c r="C96" s="6"/>
@@ -1953,7 +2521,7 @@
       <c r="K96" s="6"/>
       <c r="L96" s="6"/>
     </row>
-    <row r="97" spans="1:12" ht="42.65" customHeight="1">
+    <row r="97" spans="1:12" ht="42.6" customHeight="1">
       <c r="A97" s="6"/>
       <c r="B97" s="6"/>
       <c r="C97" s="6"/>
@@ -1967,7 +2535,7 @@
       <c r="K97" s="6"/>
       <c r="L97" s="6"/>
     </row>
-    <row r="98" spans="1:12" ht="42.65" customHeight="1">
+    <row r="98" spans="1:12" ht="42.6" customHeight="1">
       <c r="A98" s="6"/>
       <c r="B98" s="6"/>
       <c r="C98" s="6"/>
@@ -1981,7 +2549,7 @@
       <c r="K98" s="6"/>
       <c r="L98" s="6"/>
     </row>
-    <row r="99" spans="1:12" ht="42.65" customHeight="1">
+    <row r="99" spans="1:12" ht="42.6" customHeight="1">
       <c r="A99" s="6"/>
       <c r="B99" s="6"/>
       <c r="C99" s="6"/>
@@ -1995,7 +2563,7 @@
       <c r="K99" s="6"/>
       <c r="L99" s="6"/>
     </row>
-    <row r="100" spans="1:12" ht="42.65" customHeight="1">
+    <row r="100" spans="1:12" ht="42.6" customHeight="1">
       <c r="A100" s="6"/>
       <c r="B100" s="6"/>
       <c r="C100" s="6"/>
@@ -2009,7 +2577,7 @@
       <c r="K100" s="6"/>
       <c r="L100" s="6"/>
     </row>
-    <row r="101" spans="1:12" ht="42.65" customHeight="1">
+    <row r="101" spans="1:12" ht="42.6" customHeight="1">
       <c r="A101" s="6"/>
       <c r="B101" s="6"/>
       <c r="C101" s="6"/>
@@ -2023,7 +2591,7 @@
       <c r="K101" s="6"/>
       <c r="L101" s="6"/>
     </row>
-    <row r="102" spans="1:12" ht="42.65" customHeight="1">
+    <row r="102" spans="1:12" ht="42.6" customHeight="1">
       <c r="A102" s="6"/>
       <c r="B102" s="6"/>
       <c r="C102" s="6"/>
@@ -2037,7 +2605,7 @@
       <c r="K102" s="6"/>
       <c r="L102" s="6"/>
     </row>
-    <row r="103" spans="1:12" ht="42.65" customHeight="1">
+    <row r="103" spans="1:12" ht="42.6" customHeight="1">
       <c r="A103" s="6"/>
       <c r="B103" s="6"/>
       <c r="C103" s="6"/>
@@ -2051,7 +2619,7 @@
       <c r="K103" s="6"/>
       <c r="L103" s="6"/>
     </row>
-    <row r="104" spans="1:12" ht="42.65" customHeight="1">
+    <row r="104" spans="1:12" ht="42.6" customHeight="1">
       <c r="A104" s="6"/>
       <c r="B104" s="6"/>
       <c r="C104" s="6"/>
@@ -2065,7 +2633,7 @@
       <c r="K104" s="6"/>
       <c r="L104" s="6"/>
     </row>
-    <row r="105" spans="1:12" ht="42.65" customHeight="1">
+    <row r="105" spans="1:12" ht="42.6" customHeight="1">
       <c r="A105" s="6"/>
       <c r="B105" s="6"/>
       <c r="C105" s="6"/>
@@ -2079,7 +2647,7 @@
       <c r="K105" s="6"/>
       <c r="L105" s="6"/>
     </row>
-    <row r="106" spans="1:12" ht="42.65" customHeight="1">
+    <row r="106" spans="1:12" ht="42.6" customHeight="1">
       <c r="A106" s="6"/>
       <c r="B106" s="6"/>
       <c r="C106" s="6"/>
@@ -2093,7 +2661,7 @@
       <c r="K106" s="6"/>
       <c r="L106" s="6"/>
     </row>
-    <row r="107" spans="1:12" ht="42.65" customHeight="1">
+    <row r="107" spans="1:12" ht="42.6" customHeight="1">
       <c r="A107" s="6"/>
       <c r="B107" s="6"/>
       <c r="C107" s="6"/>
@@ -2107,7 +2675,7 @@
       <c r="K107" s="6"/>
       <c r="L107" s="6"/>
     </row>
-    <row r="108" spans="1:12" ht="42.65" customHeight="1">
+    <row r="108" spans="1:12" ht="42.6" customHeight="1">
       <c r="A108" s="6"/>
       <c r="B108" s="6"/>
       <c r="C108" s="6"/>
@@ -2121,7 +2689,7 @@
       <c r="K108" s="6"/>
       <c r="L108" s="6"/>
     </row>
-    <row r="109" spans="1:12" ht="42.65" customHeight="1">
+    <row r="109" spans="1:12" ht="42.6" customHeight="1">
       <c r="A109" s="6"/>
       <c r="B109" s="6"/>
       <c r="C109" s="6"/>
@@ -2135,7 +2703,7 @@
       <c r="K109" s="6"/>
       <c r="L109" s="6"/>
     </row>
-    <row r="110" spans="1:12" ht="42.65" customHeight="1">
+    <row r="110" spans="1:12" ht="42.6" customHeight="1">
       <c r="A110" s="6"/>
       <c r="B110" s="6"/>
       <c r="C110" s="6"/>
@@ -2149,7 +2717,7 @@
       <c r="K110" s="6"/>
       <c r="L110" s="6"/>
     </row>
-    <row r="111" spans="1:12" ht="42.65" customHeight="1">
+    <row r="111" spans="1:12" ht="42.6" customHeight="1">
       <c r="A111" s="6"/>
       <c r="B111" s="6"/>
       <c r="C111" s="6"/>
@@ -2163,7 +2731,7 @@
       <c r="K111" s="6"/>
       <c r="L111" s="6"/>
     </row>
-    <row r="112" spans="1:12" ht="42.65" customHeight="1">
+    <row r="112" spans="1:12" ht="42.6" customHeight="1">
       <c r="A112" s="6"/>
       <c r="B112" s="6"/>
       <c r="C112" s="6"/>
@@ -2177,7 +2745,7 @@
       <c r="K112" s="6"/>
       <c r="L112" s="6"/>
     </row>
-    <row r="113" spans="1:12" ht="42.65" customHeight="1">
+    <row r="113" spans="1:12" ht="42.6" customHeight="1">
       <c r="A113" s="6"/>
       <c r="B113" s="6"/>
       <c r="C113" s="6"/>
@@ -2191,7 +2759,7 @@
       <c r="K113" s="6"/>
       <c r="L113" s="6"/>
     </row>
-    <row r="114" spans="1:12" ht="42.65" customHeight="1">
+    <row r="114" spans="1:12" ht="42.6" customHeight="1">
       <c r="A114" s="6"/>
       <c r="B114" s="6"/>
       <c r="C114" s="6"/>
@@ -2205,7 +2773,7 @@
       <c r="K114" s="6"/>
       <c r="L114" s="6"/>
     </row>
-    <row r="115" spans="1:12" ht="42.65" customHeight="1">
+    <row r="115" spans="1:12" ht="42.6" customHeight="1">
       <c r="A115" s="6"/>
       <c r="B115" s="6"/>
       <c r="C115" s="6"/>
@@ -2219,7 +2787,7 @@
       <c r="K115" s="6"/>
       <c r="L115" s="6"/>
     </row>
-    <row r="116" spans="1:12" ht="42.65" customHeight="1">
+    <row r="116" spans="1:12" ht="42.6" customHeight="1">
       <c r="A116" s="6"/>
       <c r="B116" s="6"/>
       <c r="C116" s="6"/>
@@ -2233,7 +2801,7 @@
       <c r="K116" s="6"/>
       <c r="L116" s="6"/>
     </row>
-    <row r="117" spans="1:12" ht="42.65" customHeight="1">
+    <row r="117" spans="1:12" ht="42.6" customHeight="1">
       <c r="A117" s="6"/>
       <c r="B117" s="6"/>
       <c r="C117" s="6"/>
@@ -2247,7 +2815,7 @@
       <c r="K117" s="6"/>
       <c r="L117" s="6"/>
     </row>
-    <row r="118" spans="1:12" ht="42.65" customHeight="1">
+    <row r="118" spans="1:12" ht="42.6" customHeight="1">
       <c r="A118" s="6"/>
       <c r="B118" s="6"/>
       <c r="C118" s="6"/>
@@ -2261,7 +2829,7 @@
       <c r="K118" s="6"/>
       <c r="L118" s="6"/>
     </row>
-    <row r="119" spans="1:12" ht="42.65" customHeight="1">
+    <row r="119" spans="1:12" ht="42.6" customHeight="1">
       <c r="A119" s="6"/>
       <c r="B119" s="6"/>
       <c r="C119" s="6"/>
@@ -2275,7 +2843,7 @@
       <c r="K119" s="6"/>
       <c r="L119" s="6"/>
     </row>
-    <row r="120" spans="1:12" ht="42.65" customHeight="1">
+    <row r="120" spans="1:12" ht="42.6" customHeight="1">
       <c r="A120" s="6"/>
       <c r="B120" s="6"/>
       <c r="C120" s="6"/>
@@ -2289,7 +2857,7 @@
       <c r="K120" s="6"/>
       <c r="L120" s="6"/>
     </row>
-    <row r="121" spans="1:12" ht="42.65" customHeight="1">
+    <row r="121" spans="1:12" ht="42.6" customHeight="1">
       <c r="A121" s="6"/>
       <c r="B121" s="6"/>
       <c r="C121" s="6"/>
@@ -2303,7 +2871,7 @@
       <c r="K121" s="6"/>
       <c r="L121" s="6"/>
     </row>
-    <row r="122" spans="1:12" ht="42.65" customHeight="1">
+    <row r="122" spans="1:12" ht="42.6" customHeight="1">
       <c r="A122" s="6"/>
       <c r="B122" s="6"/>
       <c r="C122" s="6"/>
@@ -2317,7 +2885,7 @@
       <c r="K122" s="6"/>
       <c r="L122" s="6"/>
     </row>
-    <row r="123" spans="1:12" ht="42.65" customHeight="1">
+    <row r="123" spans="1:12" ht="42.6" customHeight="1">
       <c r="A123" s="6"/>
       <c r="B123" s="6"/>
       <c r="C123" s="6"/>
@@ -2331,7 +2899,7 @@
       <c r="K123" s="6"/>
       <c r="L123" s="6"/>
     </row>
-    <row r="124" spans="1:12" ht="42.65" customHeight="1">
+    <row r="124" spans="1:12" ht="42.6" customHeight="1">
       <c r="A124" s="6"/>
       <c r="B124" s="6"/>
       <c r="C124" s="6"/>
@@ -2345,7 +2913,7 @@
       <c r="K124" s="6"/>
       <c r="L124" s="6"/>
     </row>
-    <row r="125" spans="1:12" ht="42.65" customHeight="1">
+    <row r="125" spans="1:12" ht="42.6" customHeight="1">
       <c r="A125" s="6"/>
       <c r="B125" s="6"/>
       <c r="C125" s="6"/>
@@ -2359,7 +2927,7 @@
       <c r="K125" s="6"/>
       <c r="L125" s="6"/>
     </row>
-    <row r="126" spans="1:12" ht="42.65" customHeight="1">
+    <row r="126" spans="1:12" ht="42.6" customHeight="1">
       <c r="A126" s="6"/>
       <c r="B126" s="6"/>
       <c r="C126" s="6"/>
@@ -2373,7 +2941,7 @@
       <c r="K126" s="6"/>
       <c r="L126" s="6"/>
     </row>
-    <row r="127" spans="1:12" ht="42.65" customHeight="1">
+    <row r="127" spans="1:12" ht="42.6" customHeight="1">
       <c r="A127" s="6"/>
       <c r="B127" s="6"/>
       <c r="C127" s="6"/>
@@ -2387,7 +2955,7 @@
       <c r="K127" s="6"/>
       <c r="L127" s="6"/>
     </row>
-    <row r="128" spans="1:12" ht="42.65" customHeight="1">
+    <row r="128" spans="1:12" ht="42.6" customHeight="1">
       <c r="A128" s="6"/>
       <c r="B128" s="6"/>
       <c r="C128" s="6"/>
@@ -2401,7 +2969,7 @@
       <c r="K128" s="6"/>
       <c r="L128" s="6"/>
     </row>
-    <row r="129" spans="1:12" ht="42.65" customHeight="1">
+    <row r="129" spans="1:12" ht="42.6" customHeight="1">
       <c r="A129" s="6"/>
       <c r="B129" s="6"/>
       <c r="C129" s="6"/>
@@ -2415,7 +2983,7 @@
       <c r="K129" s="6"/>
       <c r="L129" s="6"/>
     </row>
-    <row r="130" spans="1:12" ht="42.65" customHeight="1">
+    <row r="130" spans="1:12" ht="42.6" customHeight="1">
       <c r="A130" s="6"/>
       <c r="B130" s="6"/>
       <c r="C130" s="6"/>
@@ -2429,7 +2997,7 @@
       <c r="K130" s="6"/>
       <c r="L130" s="6"/>
     </row>
-    <row r="131" spans="1:12" ht="42.65" customHeight="1">
+    <row r="131" spans="1:12" ht="42.6" customHeight="1">
       <c r="A131" s="6"/>
       <c r="B131" s="6"/>
       <c r="C131" s="6"/>
@@ -2443,7 +3011,7 @@
       <c r="K131" s="6"/>
       <c r="L131" s="6"/>
     </row>
-    <row r="132" spans="1:12" ht="42.65" customHeight="1">
+    <row r="132" spans="1:12" ht="42.6" customHeight="1">
       <c r="A132" s="6"/>
       <c r="B132" s="6"/>
       <c r="C132" s="6"/>
@@ -2457,7 +3025,7 @@
       <c r="K132" s="6"/>
       <c r="L132" s="6"/>
     </row>
-    <row r="133" spans="1:12" ht="42.65" customHeight="1">
+    <row r="133" spans="1:12" ht="42.6" customHeight="1">
       <c r="A133" s="6"/>
       <c r="B133" s="6"/>
       <c r="C133" s="6"/>
@@ -2471,7 +3039,7 @@
       <c r="K133" s="6"/>
       <c r="L133" s="6"/>
     </row>
-    <row r="134" spans="1:12" ht="42.65" customHeight="1">
+    <row r="134" spans="1:12" ht="42.6" customHeight="1">
       <c r="A134" s="6"/>
       <c r="B134" s="6"/>
       <c r="C134" s="6"/>
@@ -2485,7 +3053,7 @@
       <c r="K134" s="6"/>
       <c r="L134" s="6"/>
     </row>
-    <row r="135" spans="1:12" ht="42.65" customHeight="1">
+    <row r="135" spans="1:12" ht="42.6" customHeight="1">
       <c r="A135" s="6"/>
       <c r="B135" s="6"/>
       <c r="C135" s="6"/>
@@ -2499,7 +3067,7 @@
       <c r="K135" s="6"/>
       <c r="L135" s="6"/>
     </row>
-    <row r="136" spans="1:12" ht="42.65" customHeight="1">
+    <row r="136" spans="1:12" ht="42.6" customHeight="1">
       <c r="A136" s="6"/>
       <c r="B136" s="6"/>
       <c r="C136" s="6"/>
@@ -2513,7 +3081,7 @@
       <c r="K136" s="6"/>
       <c r="L136" s="6"/>
     </row>
-    <row r="137" spans="1:12" ht="42.65" customHeight="1">
+    <row r="137" spans="1:12" ht="42.6" customHeight="1">
       <c r="A137" s="6"/>
       <c r="B137" s="6"/>
       <c r="C137" s="6"/>
@@ -2527,7 +3095,7 @@
       <c r="K137" s="6"/>
       <c r="L137" s="6"/>
     </row>
-    <row r="138" spans="1:12" ht="42.65" customHeight="1">
+    <row r="138" spans="1:12" ht="42.6" customHeight="1">
       <c r="A138" s="6"/>
       <c r="B138" s="6"/>
       <c r="C138" s="6"/>
@@ -2541,7 +3109,7 @@
       <c r="K138" s="6"/>
       <c r="L138" s="6"/>
     </row>
-    <row r="139" spans="1:12" ht="42.65" customHeight="1">
+    <row r="139" spans="1:12" ht="42.6" customHeight="1">
       <c r="A139" s="6"/>
       <c r="B139" s="6"/>
       <c r="C139" s="6"/>
@@ -2555,7 +3123,7 @@
       <c r="K139" s="6"/>
       <c r="L139" s="6"/>
     </row>
-    <row r="140" spans="1:12" ht="42.65" customHeight="1">
+    <row r="140" spans="1:12" ht="42.6" customHeight="1">
       <c r="A140" s="6"/>
       <c r="B140" s="6"/>
       <c r="C140" s="6"/>
@@ -2569,7 +3137,7 @@
       <c r="K140" s="6"/>
       <c r="L140" s="6"/>
     </row>
-    <row r="141" spans="1:12" ht="42.65" customHeight="1">
+    <row r="141" spans="1:12" ht="42.6" customHeight="1">
       <c r="A141" s="6"/>
       <c r="B141" s="6"/>
       <c r="C141" s="6"/>
@@ -2583,7 +3151,7 @@
       <c r="K141" s="6"/>
       <c r="L141" s="6"/>
     </row>
-    <row r="142" spans="1:12" ht="42.65" customHeight="1">
+    <row r="142" spans="1:12" ht="42.6" customHeight="1">
       <c r="A142" s="6"/>
       <c r="B142" s="6"/>
       <c r="C142" s="6"/>
@@ -2597,7 +3165,7 @@
       <c r="K142" s="6"/>
       <c r="L142" s="6"/>
     </row>
-    <row r="143" spans="1:12" ht="42.65" customHeight="1">
+    <row r="143" spans="1:12" ht="42.6" customHeight="1">
       <c r="A143" s="6"/>
       <c r="B143" s="6"/>
       <c r="C143" s="6"/>
@@ -2611,7 +3179,7 @@
       <c r="K143" s="6"/>
       <c r="L143" s="6"/>
     </row>
-    <row r="144" spans="1:12" ht="42.65" customHeight="1">
+    <row r="144" spans="1:12" ht="42.6" customHeight="1">
       <c r="A144" s="6"/>
       <c r="B144" s="6"/>
       <c r="C144" s="6"/>
@@ -2625,7 +3193,7 @@
       <c r="K144" s="6"/>
       <c r="L144" s="6"/>
     </row>
-    <row r="145" spans="1:12" ht="42.65" customHeight="1">
+    <row r="145" spans="1:12" ht="42.6" customHeight="1">
       <c r="A145" s="6"/>
       <c r="B145" s="6"/>
       <c r="C145" s="6"/>
@@ -2639,7 +3207,7 @@
       <c r="K145" s="6"/>
       <c r="L145" s="6"/>
     </row>
-    <row r="146" spans="1:12" ht="42.65" customHeight="1">
+    <row r="146" spans="1:12" ht="42.6" customHeight="1">
       <c r="A146" s="6"/>
       <c r="B146" s="6"/>
       <c r="C146" s="6"/>
@@ -2653,7 +3221,7 @@
       <c r="K146" s="6"/>
       <c r="L146" s="6"/>
     </row>
-    <row r="147" spans="1:12" ht="42.65" customHeight="1">
+    <row r="147" spans="1:12" ht="42.6" customHeight="1">
       <c r="A147" s="6"/>
       <c r="B147" s="6"/>
       <c r="C147" s="6"/>
@@ -2667,7 +3235,7 @@
       <c r="K147" s="6"/>
       <c r="L147" s="6"/>
     </row>
-    <row r="148" spans="1:12" ht="42.65" customHeight="1">
+    <row r="148" spans="1:12" ht="42.6" customHeight="1">
       <c r="A148" s="6"/>
       <c r="B148" s="6"/>
       <c r="C148" s="6"/>
@@ -2681,7 +3249,7 @@
       <c r="K148" s="6"/>
       <c r="L148" s="6"/>
     </row>
-    <row r="149" spans="1:12" ht="42.65" customHeight="1">
+    <row r="149" spans="1:12" ht="42.6" customHeight="1">
       <c r="A149" s="6"/>
       <c r="B149" s="6"/>
       <c r="C149" s="6"/>
@@ -2695,7 +3263,7 @@
       <c r="K149" s="6"/>
       <c r="L149" s="6"/>
     </row>
-    <row r="150" spans="1:12" ht="42.65" customHeight="1">
+    <row r="150" spans="1:12" ht="42.6" customHeight="1">
       <c r="A150" s="6"/>
       <c r="B150" s="6"/>
       <c r="C150" s="6"/>
@@ -2709,7 +3277,7 @@
       <c r="K150" s="6"/>
       <c r="L150" s="6"/>
     </row>
-    <row r="151" spans="1:12" ht="42.65" customHeight="1">
+    <row r="151" spans="1:12" ht="42.6" customHeight="1">
       <c r="A151" s="6"/>
       <c r="B151" s="6"/>
       <c r="C151" s="6"/>
@@ -2723,7 +3291,7 @@
       <c r="K151" s="6"/>
       <c r="L151" s="6"/>
     </row>
-    <row r="152" spans="1:12" ht="42.65" customHeight="1">
+    <row r="152" spans="1:12" ht="42.6" customHeight="1">
       <c r="A152" s="6"/>
       <c r="B152" s="6"/>
       <c r="C152" s="6"/>
@@ -2737,7 +3305,7 @@
       <c r="K152" s="6"/>
       <c r="L152" s="6"/>
     </row>
-    <row r="153" spans="1:12" ht="42.65" customHeight="1">
+    <row r="153" spans="1:12" ht="42.6" customHeight="1">
       <c r="A153" s="6"/>
       <c r="B153" s="6"/>
       <c r="C153" s="6"/>
@@ -2751,7 +3319,7 @@
       <c r="K153" s="6"/>
       <c r="L153" s="6"/>
     </row>
-    <row r="154" spans="1:12" ht="42.65" customHeight="1">
+    <row r="154" spans="1:12" ht="42.6" customHeight="1">
       <c r="A154" s="6"/>
       <c r="B154" s="6"/>
       <c r="C154" s="6"/>
@@ -2765,7 +3333,7 @@
       <c r="K154" s="6"/>
       <c r="L154" s="6"/>
     </row>
-    <row r="155" spans="1:12" ht="42.65" customHeight="1">
+    <row r="155" spans="1:12" ht="42.6" customHeight="1">
       <c r="A155" s="6"/>
       <c r="B155" s="6"/>
       <c r="C155" s="6"/>
@@ -2779,7 +3347,7 @@
       <c r="K155" s="6"/>
       <c r="L155" s="6"/>
     </row>
-    <row r="156" spans="1:12" ht="42.65" customHeight="1">
+    <row r="156" spans="1:12" ht="42.6" customHeight="1">
       <c r="A156" s="6"/>
       <c r="B156" s="6"/>
       <c r="C156" s="6"/>
@@ -2793,7 +3361,7 @@
       <c r="K156" s="6"/>
       <c r="L156" s="6"/>
     </row>
-    <row r="157" spans="1:12" ht="42.65" customHeight="1">
+    <row r="157" spans="1:12" ht="42.6" customHeight="1">
       <c r="A157" s="6"/>
       <c r="B157" s="6"/>
       <c r="C157" s="6"/>
@@ -2807,7 +3375,7 @@
       <c r="K157" s="6"/>
       <c r="L157" s="6"/>
     </row>
-    <row r="158" spans="1:12" ht="42.65" customHeight="1">
+    <row r="158" spans="1:12" ht="42.6" customHeight="1">
       <c r="A158" s="6"/>
       <c r="B158" s="6"/>
       <c r="C158" s="6"/>
@@ -2821,7 +3389,7 @@
       <c r="K158" s="6"/>
       <c r="L158" s="6"/>
     </row>
-    <row r="159" spans="1:12" ht="42.65" customHeight="1">
+    <row r="159" spans="1:12" ht="42.6" customHeight="1">
       <c r="A159" s="6"/>
       <c r="B159" s="6"/>
       <c r="C159" s="6"/>
@@ -2835,7 +3403,7 @@
       <c r="K159" s="6"/>
       <c r="L159" s="6"/>
     </row>
-    <row r="160" spans="1:12" ht="42.65" customHeight="1">
+    <row r="160" spans="1:12" ht="42.6" customHeight="1">
       <c r="A160" s="6"/>
       <c r="B160" s="6"/>
       <c r="C160" s="6"/>
@@ -2849,7 +3417,7 @@
       <c r="K160" s="6"/>
       <c r="L160" s="6"/>
     </row>
-    <row r="161" spans="1:12" ht="42.65" customHeight="1">
+    <row r="161" spans="1:12" ht="42.6" customHeight="1">
       <c r="A161" s="6"/>
       <c r="B161" s="6"/>
       <c r="C161" s="6"/>
@@ -2863,7 +3431,7 @@
       <c r="K161" s="6"/>
       <c r="L161" s="6"/>
     </row>
-    <row r="162" spans="1:12" ht="42.65" customHeight="1">
+    <row r="162" spans="1:12" ht="42.6" customHeight="1">
       <c r="A162" s="6"/>
       <c r="B162" s="6"/>
       <c r="C162" s="6"/>
@@ -2877,7 +3445,7 @@
       <c r="K162" s="6"/>
       <c r="L162" s="6"/>
     </row>
-    <row r="163" spans="1:12" ht="42.65" customHeight="1">
+    <row r="163" spans="1:12" ht="42.6" customHeight="1">
       <c r="A163" s="6"/>
       <c r="B163" s="6"/>
       <c r="C163" s="6"/>
@@ -2891,7 +3459,7 @@
       <c r="K163" s="6"/>
       <c r="L163" s="6"/>
     </row>
-    <row r="164" spans="1:12" ht="42.65" customHeight="1">
+    <row r="164" spans="1:12" ht="42.6" customHeight="1">
       <c r="A164" s="6"/>
       <c r="B164" s="6"/>
       <c r="C164" s="6"/>
@@ -2905,7 +3473,7 @@
       <c r="K164" s="6"/>
       <c r="L164" s="6"/>
     </row>
-    <row r="165" spans="1:12" ht="42.65" customHeight="1">
+    <row r="165" spans="1:12" ht="42.6" customHeight="1">
       <c r="A165" s="6"/>
       <c r="B165" s="6"/>
       <c r="C165" s="6"/>
@@ -2919,7 +3487,7 @@
       <c r="K165" s="6"/>
       <c r="L165" s="6"/>
     </row>
-    <row r="166" spans="1:12" ht="42.65" customHeight="1">
+    <row r="166" spans="1:12" ht="42.6" customHeight="1">
       <c r="A166" s="6"/>
       <c r="B166" s="6"/>
       <c r="C166" s="6"/>
@@ -2933,7 +3501,7 @@
       <c r="K166" s="6"/>
       <c r="L166" s="6"/>
     </row>
-    <row r="167" spans="1:12" ht="42.65" customHeight="1">
+    <row r="167" spans="1:12" ht="42.6" customHeight="1">
       <c r="A167" s="6"/>
       <c r="B167" s="6"/>
       <c r="C167" s="6"/>
@@ -2947,7 +3515,7 @@
       <c r="K167" s="6"/>
       <c r="L167" s="6"/>
     </row>
-    <row r="168" spans="1:12" ht="42.65" customHeight="1">
+    <row r="168" spans="1:12" ht="42.6" customHeight="1">
       <c r="A168" s="6"/>
       <c r="B168" s="6"/>
       <c r="C168" s="6"/>
@@ -2961,7 +3529,7 @@
       <c r="K168" s="6"/>
       <c r="L168" s="6"/>
     </row>
-    <row r="169" spans="1:12" ht="42.65" customHeight="1">
+    <row r="169" spans="1:12" ht="42.6" customHeight="1">
       <c r="A169" s="6"/>
       <c r="B169" s="6"/>
       <c r="C169" s="6"/>
@@ -2975,7 +3543,7 @@
       <c r="K169" s="6"/>
       <c r="L169" s="6"/>
     </row>
-    <row r="170" spans="1:12" ht="42.65" customHeight="1">
+    <row r="170" spans="1:12" ht="42.6" customHeight="1">
       <c r="A170" s="6"/>
       <c r="B170" s="6"/>
       <c r="C170" s="6"/>
@@ -2989,7 +3557,7 @@
       <c r="K170" s="6"/>
       <c r="L170" s="6"/>
     </row>
-    <row r="171" spans="1:12" ht="42.65" customHeight="1">
+    <row r="171" spans="1:12" ht="42.6" customHeight="1">
       <c r="A171" s="6"/>
       <c r="B171" s="6"/>
       <c r="C171" s="6"/>
@@ -3003,7 +3571,7 @@
       <c r="K171" s="6"/>
       <c r="L171" s="6"/>
     </row>
-    <row r="172" spans="1:12" ht="42.65" customHeight="1">
+    <row r="172" spans="1:12" ht="42.6" customHeight="1">
       <c r="A172" s="6"/>
       <c r="B172" s="6"/>
       <c r="C172" s="6"/>
@@ -3017,7 +3585,7 @@
       <c r="K172" s="6"/>
       <c r="L172" s="6"/>
     </row>
-    <row r="173" spans="1:12" ht="42.65" customHeight="1">
+    <row r="173" spans="1:12" ht="42.6" customHeight="1">
       <c r="A173" s="6"/>
       <c r="B173" s="6"/>
       <c r="C173" s="6"/>
@@ -3031,7 +3599,7 @@
       <c r="K173" s="6"/>
       <c r="L173" s="6"/>
     </row>
-    <row r="174" spans="1:12" ht="42.65" customHeight="1">
+    <row r="174" spans="1:12" ht="42.6" customHeight="1">
       <c r="A174" s="6"/>
       <c r="B174" s="6"/>
       <c r="C174" s="6"/>
@@ -3045,7 +3613,7 @@
       <c r="K174" s="6"/>
       <c r="L174" s="6"/>
     </row>
-    <row r="175" spans="1:12" ht="42.65" customHeight="1">
+    <row r="175" spans="1:12" ht="42.6" customHeight="1">
       <c r="A175" s="6"/>
       <c r="B175" s="6"/>
       <c r="C175" s="6"/>
@@ -3059,7 +3627,7 @@
       <c r="K175" s="6"/>
       <c r="L175" s="6"/>
     </row>
-    <row r="176" spans="1:12" ht="42.65" customHeight="1">
+    <row r="176" spans="1:12" ht="42.6" customHeight="1">
       <c r="A176" s="6"/>
       <c r="B176" s="6"/>
       <c r="C176" s="6"/>
@@ -3073,7 +3641,7 @@
       <c r="K176" s="6"/>
       <c r="L176" s="6"/>
     </row>
-    <row r="177" spans="1:12" ht="42.65" customHeight="1">
+    <row r="177" spans="1:12" ht="42.6" customHeight="1">
       <c r="A177" s="6"/>
       <c r="B177" s="6"/>
       <c r="C177" s="6"/>
@@ -3087,7 +3655,7 @@
       <c r="K177" s="6"/>
       <c r="L177" s="6"/>
     </row>
-    <row r="178" spans="1:12" ht="42.65" customHeight="1">
+    <row r="178" spans="1:12" ht="42.6" customHeight="1">
       <c r="A178" s="6"/>
       <c r="B178" s="6"/>
       <c r="C178" s="6"/>
@@ -3101,7 +3669,7 @@
       <c r="K178" s="6"/>
       <c r="L178" s="6"/>
     </row>
-    <row r="179" spans="1:12" ht="42.65" customHeight="1">
+    <row r="179" spans="1:12" ht="42.6" customHeight="1">
       <c r="A179" s="6"/>
       <c r="B179" s="6"/>
       <c r="C179" s="6"/>
@@ -3115,7 +3683,7 @@
       <c r="K179" s="6"/>
       <c r="L179" s="6"/>
     </row>
-    <row r="180" spans="1:12" ht="42.65" customHeight="1">
+    <row r="180" spans="1:12" ht="42.6" customHeight="1">
       <c r="A180" s="6"/>
       <c r="B180" s="6"/>
       <c r="C180" s="6"/>
@@ -3129,7 +3697,7 @@
       <c r="K180" s="6"/>
       <c r="L180" s="6"/>
     </row>
-    <row r="181" spans="1:12" ht="42.65" customHeight="1">
+    <row r="181" spans="1:12" ht="42.6" customHeight="1">
       <c r="A181" s="6"/>
       <c r="B181" s="6"/>
       <c r="C181" s="6"/>
@@ -3143,7 +3711,7 @@
       <c r="K181" s="6"/>
       <c r="L181" s="6"/>
     </row>
-    <row r="182" spans="1:12" ht="42.65" customHeight="1">
+    <row r="182" spans="1:12" ht="42.6" customHeight="1">
       <c r="A182" s="6"/>
       <c r="B182" s="6"/>
       <c r="C182" s="6"/>
@@ -3157,7 +3725,7 @@
       <c r="K182" s="6"/>
       <c r="L182" s="6"/>
     </row>
-    <row r="183" spans="1:12" ht="42.65" customHeight="1">
+    <row r="183" spans="1:12" ht="42.6" customHeight="1">
       <c r="A183" s="6"/>
       <c r="B183" s="6"/>
       <c r="C183" s="6"/>
@@ -3171,7 +3739,7 @@
       <c r="K183" s="6"/>
       <c r="L183" s="6"/>
     </row>
-    <row r="184" spans="1:12" ht="42.65" customHeight="1">
+    <row r="184" spans="1:12" ht="42.6" customHeight="1">
       <c r="A184" s="6"/>
       <c r="B184" s="6"/>
       <c r="C184" s="6"/>
@@ -3185,7 +3753,7 @@
       <c r="K184" s="6"/>
       <c r="L184" s="6"/>
     </row>
-    <row r="185" spans="1:12" ht="42.65" customHeight="1">
+    <row r="185" spans="1:12" ht="42.6" customHeight="1">
       <c r="A185" s="6"/>
       <c r="B185" s="6"/>
       <c r="C185" s="6"/>
@@ -3199,7 +3767,7 @@
       <c r="K185" s="6"/>
       <c r="L185" s="6"/>
     </row>
-    <row r="186" spans="1:12" ht="42.65" customHeight="1">
+    <row r="186" spans="1:12" ht="42.6" customHeight="1">
       <c r="A186" s="6"/>
       <c r="B186" s="6"/>
       <c r="C186" s="6"/>
@@ -3213,7 +3781,7 @@
       <c r="K186" s="6"/>
       <c r="L186" s="6"/>
     </row>
-    <row r="187" spans="1:12" ht="42.65" customHeight="1">
+    <row r="187" spans="1:12" ht="42.6" customHeight="1">
       <c r="A187" s="6"/>
       <c r="B187" s="6"/>
       <c r="C187" s="6"/>
@@ -3227,7 +3795,7 @@
       <c r="K187" s="6"/>
       <c r="L187" s="6"/>
     </row>
-    <row r="188" spans="1:12" ht="42.65" customHeight="1">
+    <row r="188" spans="1:12" ht="42.6" customHeight="1">
       <c r="A188" s="6"/>
       <c r="B188" s="6"/>
       <c r="C188" s="6"/>
@@ -3241,7 +3809,7 @@
       <c r="K188" s="6"/>
       <c r="L188" s="6"/>
     </row>
-    <row r="189" spans="1:12" ht="42.65" customHeight="1">
+    <row r="189" spans="1:12" ht="42.6" customHeight="1">
       <c r="A189" s="6"/>
       <c r="B189" s="6"/>
       <c r="C189" s="6"/>
@@ -3255,7 +3823,7 @@
       <c r="K189" s="6"/>
       <c r="L189" s="6"/>
     </row>
-    <row r="190" spans="1:12" ht="42.65" customHeight="1">
+    <row r="190" spans="1:12" ht="42.6" customHeight="1">
       <c r="A190" s="6"/>
       <c r="B190" s="6"/>
       <c r="C190" s="6"/>
@@ -3269,7 +3837,7 @@
       <c r="K190" s="6"/>
       <c r="L190" s="6"/>
     </row>
-    <row r="191" spans="1:12" ht="42.65" customHeight="1">
+    <row r="191" spans="1:12" ht="42.6" customHeight="1">
       <c r="A191" s="6"/>
       <c r="B191" s="6"/>
       <c r="C191" s="6"/>
@@ -3283,7 +3851,7 @@
       <c r="K191" s="6"/>
       <c r="L191" s="6"/>
     </row>
-    <row r="192" spans="1:12" ht="42.65" customHeight="1">
+    <row r="192" spans="1:12" ht="42.6" customHeight="1">
       <c r="A192" s="6"/>
       <c r="B192" s="6"/>
       <c r="C192" s="6"/>
@@ -3297,7 +3865,7 @@
       <c r="K192" s="6"/>
       <c r="L192" s="6"/>
     </row>
-    <row r="193" spans="1:12" ht="42.65" customHeight="1">
+    <row r="193" spans="1:12" ht="42.6" customHeight="1">
       <c r="A193" s="6"/>
       <c r="B193" s="6"/>
       <c r="C193" s="6"/>
@@ -3311,7 +3879,7 @@
       <c r="K193" s="6"/>
       <c r="L193" s="6"/>
     </row>
-    <row r="194" spans="1:12" ht="42.65" customHeight="1">
+    <row r="194" spans="1:12" ht="42.6" customHeight="1">
       <c r="A194" s="6"/>
       <c r="B194" s="6"/>
       <c r="C194" s="6"/>
@@ -3325,7 +3893,7 @@
       <c r="K194" s="6"/>
       <c r="L194" s="6"/>
     </row>
-    <row r="195" spans="1:12" ht="42.65" customHeight="1">
+    <row r="195" spans="1:12" ht="42.6" customHeight="1">
       <c r="A195" s="6"/>
       <c r="B195" s="6"/>
       <c r="C195" s="6"/>
@@ -3339,7 +3907,7 @@
       <c r="K195" s="6"/>
       <c r="L195" s="6"/>
     </row>
-    <row r="196" spans="1:12" ht="42.65" customHeight="1">
+    <row r="196" spans="1:12" ht="42.6" customHeight="1">
       <c r="A196" s="6"/>
       <c r="B196" s="6"/>
       <c r="C196" s="6"/>
@@ -3353,7 +3921,7 @@
       <c r="K196" s="6"/>
       <c r="L196" s="6"/>
     </row>
-    <row r="197" spans="1:12" ht="42.65" customHeight="1">
+    <row r="197" spans="1:12" ht="42.6" customHeight="1">
       <c r="A197" s="6"/>
       <c r="B197" s="6"/>
       <c r="C197" s="6"/>
@@ -3367,7 +3935,7 @@
       <c r="K197" s="6"/>
       <c r="L197" s="6"/>
     </row>
-    <row r="198" spans="1:12" ht="42.65" customHeight="1">
+    <row r="198" spans="1:12" ht="42.6" customHeight="1">
       <c r="A198" s="6"/>
       <c r="B198" s="6"/>
       <c r="C198" s="6"/>
@@ -3381,7 +3949,7 @@
       <c r="K198" s="6"/>
       <c r="L198" s="6"/>
     </row>
-    <row r="199" spans="1:12" ht="42.65" customHeight="1">
+    <row r="199" spans="1:12" ht="42.6" customHeight="1">
       <c r="A199" s="6"/>
       <c r="B199" s="6"/>
       <c r="C199" s="6"/>
@@ -3395,7 +3963,7 @@
       <c r="K199" s="6"/>
       <c r="L199" s="6"/>
     </row>
-    <row r="200" spans="1:12" ht="42.65" customHeight="1">
+    <row r="200" spans="1:12" ht="42.6" customHeight="1">
       <c r="A200" s="6"/>
       <c r="B200" s="6"/>
       <c r="C200" s="6"/>
@@ -3451,28 +4019,28 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="62" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="20">
-      <c r="A1" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
+    <row r="1" spans="1:6" ht="21">
+      <c r="A1" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
     </row>
     <row r="3" spans="1:6" ht="22.65" customHeight="1">
       <c r="A3" s="8" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="22.65" customHeight="1">
@@ -3480,7 +4048,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="22.65" customHeight="1">
@@ -3488,7 +4056,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="22.65" customHeight="1">
@@ -3496,7 +4064,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="22.65" customHeight="1">
@@ -3504,7 +4072,7 @@
         <v>10</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="22.65" customHeight="1">
@@ -3512,7 +4080,7 @@
         <v>11</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="22.65" customHeight="1">
@@ -3520,7 +4088,7 @@
         <v>12</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="22.65" customHeight="1">
@@ -3528,7 +4096,7 @@
         <v>13</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="22.65" customHeight="1">
@@ -3536,7 +4104,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="22.65" customHeight="1">
@@ -3544,7 +4112,7 @@
         <v>15</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="22.65" customHeight="1">
@@ -3552,7 +4120,7 @@
         <v>16</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="22.65" customHeight="1">
@@ -3560,7 +4128,7 @@
         <v>17</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -3568,7 +4136,7 @@
         <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -3578,4 +4146,239 @@
   <phoneticPr fontId="6"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100FFFAEB3A24D8254EA931476DB8D60440" ma:contentTypeVersion="9" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="c8d193e0f54e03b4175f5a4db63c885a">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="d50c1a2a-6294-41b5-bbeb-a77cda6c64f4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e7e962f02e8fc9ae74e529f59a05e711" ns3:_="">
+    <xsd:import namespace="d50c1a2a-6294-41b5-bbeb-a77cda6c64f4"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceSystemTags" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns3:_activity" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="d50c1a2a-6294-41b5-bbeb-a77cda6c64f4" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceDateTaken" ma:index="8" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSystemTags" ma:index="12" nillable="true" ma:displayName="MediaServiceSystemTags" ma:hidden="true" ma:internalName="MediaServiceSystemTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="_activity" ma:index="16" nillable="true" ma:displayName="_activity" ma:hidden="true" ma:internalName="_activity">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="コンテンツ タイプ"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="タイトル"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="d50c1a2a-6294-41b5-bbeb-a77cda6c64f4" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9BB742F5-3D3F-4A88-B680-F1D8F2300B9A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="d50c1a2a-6294-41b5-bbeb-a77cda6c64f4"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55C5DA50-4866-466E-A4B2-AE8F0C9C1383}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE6802ED-7940-418A-A3F2-9BAE74B9B460}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="d50c1a2a-6294-41b5-bbeb-a77cda6c64f4"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/tests/tests.xlsx
+++ b/tests/tests.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1f3453c015a41521/デスクトップ/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nymgs\team04\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD370010-200F-4853-A1FE-741A27A94439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E19B21F1-69A9-4BFA-A405-B21F68656396}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="テスト記録" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="118">
   <si>
     <t>ゲーム動作テスト記録</t>
   </si>
@@ -595,6 +595,422 @@
     </rPh>
     <rPh sb="7" eb="8">
       <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>02-1</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>02-2</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>02-3</t>
+  </si>
+  <si>
+    <t>02-4</t>
+  </si>
+  <si>
+    <t>02-5</t>
+  </si>
+  <si>
+    <t>02-6</t>
+  </si>
+  <si>
+    <t>野村侑来</t>
+    <rPh sb="0" eb="2">
+      <t>ノムラ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ユウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>ゲーム中</t>
+    <rPh sb="3" eb="4">
+      <t>チュウ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>アイテムに自機を触れさせる</t>
+    <rPh sb="5" eb="7">
+      <t>ジキ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>フ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>自機の移動速度が上昇する</t>
+    <rPh sb="0" eb="2">
+      <t>ジキ</t>
+    </rPh>
+    <rPh sb="3" eb="7">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジョウショウ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>自機の移動速度が戻る</t>
+    <rPh sb="0" eb="2">
+      <t>ジキ</t>
+    </rPh>
+    <rPh sb="3" eb="7">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>敵機の移動速度が低下する</t>
+    <rPh sb="0" eb="3">
+      <t>テキキ</t>
+    </rPh>
+    <rPh sb="3" eb="7">
+      <t>イドウソクド</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>テイカ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>敵機の移動速度が戻る</t>
+    <rPh sb="0" eb="2">
+      <t>テキキ</t>
+    </rPh>
+    <rPh sb="3" eb="7">
+      <t>イドウソクド</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>敵の数が減る</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>カズ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ヘ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>加速アイテムを取る</t>
+    <rPh sb="0" eb="2">
+      <t>カソク</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>加速アイテムを取った後、ゲームをリスタートする</t>
+    <rPh sb="0" eb="2">
+      <t>カソク</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ノチ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>減速アイテムを取る</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンソク</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>減速アイテムを取った後、ゲームをリスタートする</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンソク</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ノチ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>攻撃アイテムを取得する</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>シュトク</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>防御アイテム取得する</t>
+    <rPh sb="0" eb="2">
+      <t>ボウギョ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シュトク</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>防御アイテム取得後、敵に触れる</t>
+    <rPh sb="0" eb="6">
+      <t>ボウ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>シュトクゴ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>フ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>防御アイテム取得後、敵に触れた後、一定時間が経過する</t>
+    <rPh sb="0" eb="6">
+      <t>ボウ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>シュトクゴ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ノチ</t>
+    </rPh>
+    <rPh sb="17" eb="21">
+      <t>イッテイジカン</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ケイカ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>02-7</t>
+  </si>
+  <si>
+    <t>02-8</t>
+  </si>
+  <si>
+    <t>リスタート時</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>特定アイテム入手後、ゲームをリスタートする</t>
+    <rPh sb="0" eb="2">
+      <t>トクテイ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>ニュウシュゴ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>バリアの数が増える</t>
+    <rPh sb="4" eb="5">
+      <t>カズ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>フ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>特定アイテム入手後、自機を敵機に触れさせる</t>
+    <rPh sb="0" eb="2">
+      <t>トクテイ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>ニュウシュゴ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ジキ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>テキキ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>特定アイテム入手後、自機を敵機に触れさせた後、一定時間経過させる</t>
+    <rPh sb="0" eb="2">
+      <t>トクテイ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>ニュウシュゴ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ジキ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>テキキ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ノチ</t>
+    </rPh>
+    <rPh sb="23" eb="27">
+      <t>イッテイジカン</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ケイカ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>バリアの効果が無くなる</t>
+    <rPh sb="4" eb="6">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ナ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>バリアの効果が発揮し、敵に触れてもゲームオーバーにならない</t>
+    <rPh sb="4" eb="6">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ハッキ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>フ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>HARDモード時において、バリアの効果が永続となっていた。</t>
+    <rPh sb="7" eb="8">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>エイゾク</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <r>
+      <t>HARD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>モード時、バリア効果を持つ床が存在しないために、不具合が生じていた。</t>
+    </r>
+    <rPh sb="7" eb="8">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ユカ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ソンザイ</t>
+    </rPh>
+    <rPh sb="28" eb="31">
+      <t>フグアイ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ショウ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>修正済み</t>
+  </si>
+  <si>
+    <t>02-9</t>
+  </si>
+  <si>
+    <t>防御アイテム取得後、ダメージを受ける床を歩く</t>
+    <rPh sb="0" eb="2">
+      <t>ボウギョ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>シュトクゴ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ユカ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>アル</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>特定アイテム入手後、自機を特定の床に触れさせる</t>
+    <rPh sb="0" eb="9">
+      <t>トク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ジキ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>トクテイ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ユカ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>バリアが発動せず、ゲームオーバーとなる。</t>
+    <rPh sb="4" eb="6">
+      <t>ハツドウ</t>
     </rPh>
     <phoneticPr fontId="6"/>
   </si>
@@ -729,12 +1145,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -749,6 +1159,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -992,7 +1408,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L200"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -1008,21 +1424,21 @@
     <col min="12" max="12" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="19.95" customHeight="1">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:12" ht="20" customHeight="1">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
@@ -1044,18 +1460,18 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="15.6">
+    <row r="4" spans="1:12" ht="15.5">
       <c r="A4" s="2">
         <f>COUNTA(A8:A200)</f>
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B4" s="2">
         <f>COUNTIF(J8:J200,"OK")</f>
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C4" s="2">
         <f>COUNTIF(J8:J200,"不具合あり")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" s="2">
         <f>COUNTIF(J8:J200,"未実施")</f>
@@ -1063,7 +1479,7 @@
       </c>
       <c r="E4" s="3">
         <f>IF(A4=0,0,B4/A4)</f>
-        <v>1.1111111111111112</v>
+        <v>0.94444444444444442</v>
       </c>
       <c r="F4" s="4">
         <v>45857.513194444444</v>
@@ -1107,11 +1523,11 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="42.6" customHeight="1">
+    <row r="8" spans="1:12" ht="42.65" customHeight="1">
       <c r="A8" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="10" t="s">
         <v>47</v>
       </c>
       <c r="C8" s="6" t="s">
@@ -1123,13 +1539,13 @@
       <c r="E8" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="G8" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="H8" s="12" t="s">
+      <c r="H8" s="10" t="s">
         <v>44</v>
       </c>
       <c r="I8" s="6"/>
@@ -1141,11 +1557,11 @@
       </c>
       <c r="L8" s="6"/>
     </row>
-    <row r="9" spans="1:12" ht="42.6" customHeight="1">
+    <row r="9" spans="1:12" ht="42.65" customHeight="1">
       <c r="A9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="9" t="s">
         <v>40</v>
       </c>
       <c r="C9" s="6" t="s">
@@ -1157,17 +1573,17 @@
       <c r="E9" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="F9" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="G9" s="12" t="s">
+      <c r="G9" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="H9" s="13" t="s">
+      <c r="H9" s="11" t="s">
         <v>44</v>
       </c>
       <c r="I9" s="6"/>
-      <c r="J9" s="12" t="s">
+      <c r="J9" s="10" t="s">
         <v>2</v>
       </c>
       <c r="K9" s="6" t="s">
@@ -1175,11 +1591,11 @@
       </c>
       <c r="L9" s="6"/>
     </row>
-    <row r="10" spans="1:12" ht="42.6" customHeight="1">
-      <c r="A10" s="14" t="s">
+    <row r="10" spans="1:12" ht="42.65" customHeight="1">
+      <c r="A10" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="10" t="s">
         <v>46</v>
       </c>
       <c r="C10" s="6" t="s">
@@ -1191,13 +1607,13 @@
       <c r="E10" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="G10" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="H10" s="13" t="s">
+      <c r="H10" s="11" t="s">
         <v>44</v>
       </c>
       <c r="I10" s="6"/>
@@ -1207,11 +1623,11 @@
       <c r="K10" s="6"/>
       <c r="L10" s="6"/>
     </row>
-    <row r="11" spans="1:12" ht="42.6" customHeight="1">
-      <c r="A11" s="15" t="s">
+    <row r="11" spans="1:12" ht="42.65" customHeight="1">
+      <c r="A11" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="10" t="s">
         <v>52</v>
       </c>
       <c r="C11" s="6" t="s">
@@ -1223,13 +1639,13 @@
       <c r="E11" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="F11" s="13" t="s">
+      <c r="F11" s="11" t="s">
         <v>60</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="H11" s="13" t="s">
+      <c r="H11" s="11" t="s">
         <v>44</v>
       </c>
       <c r="I11" s="6"/>
@@ -1239,11 +1655,11 @@
       <c r="K11" s="6"/>
       <c r="L11" s="6"/>
     </row>
-    <row r="12" spans="1:12" ht="42.6" customHeight="1">
-      <c r="A12" s="15" t="s">
+    <row r="12" spans="1:12" ht="42.65" customHeight="1">
+      <c r="A12" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="10" t="s">
         <v>63</v>
       </c>
       <c r="C12" s="6" t="s">
@@ -1252,16 +1668,16 @@
       <c r="D12" s="7">
         <v>45857.513194444444</v>
       </c>
-      <c r="E12" s="13" t="s">
+      <c r="E12" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="F12" s="13" t="s">
+      <c r="F12" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="12" t="s">
+      <c r="G12" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="H12" s="13" t="s">
+      <c r="H12" s="11" t="s">
         <v>44</v>
       </c>
       <c r="I12" s="6"/>
@@ -1271,11 +1687,11 @@
       <c r="K12" s="6"/>
       <c r="L12" s="6"/>
     </row>
-    <row r="13" spans="1:12" ht="42.6" customHeight="1">
-      <c r="A13" s="15" t="s">
+    <row r="13" spans="1:12" ht="42.65" customHeight="1">
+      <c r="A13" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="11" t="s">
         <v>64</v>
       </c>
       <c r="C13" s="6" t="s">
@@ -1284,16 +1700,16 @@
       <c r="D13" s="7">
         <v>46223</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E13" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="F13" s="13" t="s">
+      <c r="F13" s="11" t="s">
         <v>65</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="H13" s="13" t="s">
+      <c r="H13" s="11" t="s">
         <v>44</v>
       </c>
       <c r="I13" s="6"/>
@@ -1303,11 +1719,11 @@
       <c r="K13" s="6"/>
       <c r="L13" s="6"/>
     </row>
-    <row r="14" spans="1:12" ht="42.6" customHeight="1">
-      <c r="A14" s="15" t="s">
+    <row r="14" spans="1:12" ht="42.65" customHeight="1">
+      <c r="A14" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="10" t="s">
         <v>69</v>
       </c>
       <c r="C14" s="6" t="s">
@@ -1319,13 +1735,13 @@
       <c r="E14" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="F14" s="13" t="s">
+      <c r="F14" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="G14" s="12" t="s">
+      <c r="G14" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="H14" s="13" t="s">
+      <c r="H14" s="11" t="s">
         <v>20</v>
       </c>
       <c r="I14" s="6"/>
@@ -1335,11 +1751,11 @@
       <c r="K14" s="6"/>
       <c r="L14" s="6"/>
     </row>
-    <row r="15" spans="1:12" ht="42.6" customHeight="1">
-      <c r="A15" s="15" t="s">
+    <row r="15" spans="1:12" ht="42.65" customHeight="1">
+      <c r="A15" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="10" t="s">
         <v>68</v>
       </c>
       <c r="C15" s="6" t="s">
@@ -1351,13 +1767,13 @@
       <c r="E15" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="F15" s="12" t="s">
+      <c r="F15" s="10" t="s">
         <v>76</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="H15" s="13" t="s">
+      <c r="H15" s="11" t="s">
         <v>20</v>
       </c>
       <c r="I15" s="6"/>
@@ -1367,8 +1783,8 @@
       <c r="K15" s="6"/>
       <c r="L15" s="6"/>
     </row>
-    <row r="16" spans="1:12" ht="42.6" customHeight="1">
-      <c r="A16" s="15" t="s">
+    <row r="16" spans="1:12" ht="42.65" customHeight="1">
+      <c r="A16" s="13" t="s">
         <v>59</v>
       </c>
       <c r="B16" s="6" t="s">
@@ -1389,7 +1805,7 @@
       <c r="G16" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="H16" s="13" t="s">
+      <c r="H16" s="11" t="s">
         <v>20</v>
       </c>
       <c r="I16" s="6"/>
@@ -1399,15 +1815,31 @@
       <c r="K16" s="6"/>
       <c r="L16" s="6"/>
     </row>
-    <row r="17" spans="1:12" ht="42.6" customHeight="1">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="13"/>
+    <row r="17" spans="1:12" ht="42.65" customHeight="1">
+      <c r="A17" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D17" s="7">
+        <v>46223.90625</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>20</v>
+      </c>
       <c r="I17" s="6"/>
       <c r="J17" s="6" t="s">
         <v>2</v>
@@ -1415,119 +1847,267 @@
       <c r="K17" s="6"/>
       <c r="L17" s="6"/>
     </row>
-    <row r="18" spans="1:12" ht="42.6" customHeight="1">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
+    <row r="18" spans="1:12" ht="42.65" customHeight="1">
+      <c r="A18" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D18" s="7">
+        <v>46224.90625</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>20</v>
+      </c>
       <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
+      <c r="J18" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="K18" s="6"/>
       <c r="L18" s="6"/>
     </row>
-    <row r="19" spans="1:12" ht="42.6" customHeight="1">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
+    <row r="19" spans="1:12" ht="42.65" customHeight="1">
+      <c r="A19" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D19" s="7">
+        <v>46225.90625</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>20</v>
+      </c>
       <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
+      <c r="J19" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="K19" s="6"/>
       <c r="L19" s="6"/>
     </row>
-    <row r="20" spans="1:12" ht="42.6" customHeight="1">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
+    <row r="20" spans="1:12" ht="42.65" customHeight="1">
+      <c r="A20" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D20" s="7">
+        <v>46226.90625</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="H20" s="11" t="s">
+        <v>20</v>
+      </c>
       <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
+      <c r="J20" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="K20" s="6"/>
       <c r="L20" s="6"/>
     </row>
-    <row r="21" spans="1:12" ht="42.6" customHeight="1">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
+    <row r="21" spans="1:12" ht="42.65" customHeight="1">
+      <c r="A21" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D21" s="7">
+        <v>46227.90625</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>20</v>
+      </c>
       <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
+      <c r="J21" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="K21" s="6"/>
       <c r="L21" s="6"/>
     </row>
-    <row r="22" spans="1:12" ht="42.6" customHeight="1">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
+    <row r="22" spans="1:12" ht="42.65" customHeight="1">
+      <c r="A22" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D22" s="7">
+        <v>46228.90625</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="H22" s="11" t="s">
+        <v>20</v>
+      </c>
       <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
+      <c r="J22" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="K22" s="6"/>
       <c r="L22" s="6"/>
     </row>
-    <row r="23" spans="1:12" ht="42.6" customHeight="1">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
+    <row r="23" spans="1:12" ht="42.65" customHeight="1">
+      <c r="A23" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D23" s="7">
+        <v>46229.90625</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="H23" s="11" t="s">
+        <v>20</v>
+      </c>
       <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
+      <c r="J23" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="K23" s="6"/>
       <c r="L23" s="6"/>
     </row>
-    <row r="24" spans="1:12" ht="42.6" customHeight="1">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
-      <c r="K24" s="6"/>
+    <row r="24" spans="1:12" ht="42.65" customHeight="1">
+      <c r="A24" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D24" s="7">
+        <v>46230.90625</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="K24" s="6" t="s">
+        <v>113</v>
+      </c>
       <c r="L24" s="6"/>
     </row>
-    <row r="25" spans="1:12" ht="42.6" customHeight="1">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
+    <row r="25" spans="1:12" ht="42.65" customHeight="1">
+      <c r="A25" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D25" s="7">
+        <v>46231.90625</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>44</v>
+      </c>
       <c r="I25" s="6"/>
-      <c r="J25" s="6"/>
+      <c r="J25" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="K25" s="6"/>
       <c r="L25" s="6"/>
     </row>
-    <row r="26" spans="1:12" ht="42.6" customHeight="1">
+    <row r="26" spans="1:12" ht="42.65" customHeight="1">
       <c r="A26" s="6"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
@@ -1541,7 +2121,7 @@
       <c r="K26" s="6"/>
       <c r="L26" s="6"/>
     </row>
-    <row r="27" spans="1:12" ht="42.6" customHeight="1">
+    <row r="27" spans="1:12" ht="42.65" customHeight="1">
       <c r="A27" s="6"/>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
@@ -1555,7 +2135,7 @@
       <c r="K27" s="6"/>
       <c r="L27" s="6"/>
     </row>
-    <row r="28" spans="1:12" ht="42.6" customHeight="1">
+    <row r="28" spans="1:12" ht="42.65" customHeight="1">
       <c r="A28" s="6"/>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -1569,7 +2149,7 @@
       <c r="K28" s="6"/>
       <c r="L28" s="6"/>
     </row>
-    <row r="29" spans="1:12" ht="42.6" customHeight="1">
+    <row r="29" spans="1:12" ht="42.65" customHeight="1">
       <c r="A29" s="6"/>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
@@ -1583,7 +2163,7 @@
       <c r="K29" s="6"/>
       <c r="L29" s="6"/>
     </row>
-    <row r="30" spans="1:12" ht="42.6" customHeight="1">
+    <row r="30" spans="1:12" ht="42.65" customHeight="1">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -1597,7 +2177,7 @@
       <c r="K30" s="6"/>
       <c r="L30" s="6"/>
     </row>
-    <row r="31" spans="1:12" ht="42.6" customHeight="1">
+    <row r="31" spans="1:12" ht="42.65" customHeight="1">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -1611,7 +2191,7 @@
       <c r="K31" s="6"/>
       <c r="L31" s="6"/>
     </row>
-    <row r="32" spans="1:12" ht="42.6" customHeight="1">
+    <row r="32" spans="1:12" ht="42.65" customHeight="1">
       <c r="A32" s="6"/>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
@@ -1625,7 +2205,7 @@
       <c r="K32" s="6"/>
       <c r="L32" s="6"/>
     </row>
-    <row r="33" spans="1:12" ht="42.6" customHeight="1">
+    <row r="33" spans="1:12" ht="42.65" customHeight="1">
       <c r="A33" s="6"/>
       <c r="B33" s="6"/>
       <c r="C33" s="6"/>
@@ -1639,7 +2219,7 @@
       <c r="K33" s="6"/>
       <c r="L33" s="6"/>
     </row>
-    <row r="34" spans="1:12" ht="42.6" customHeight="1">
+    <row r="34" spans="1:12" ht="42.65" customHeight="1">
       <c r="A34" s="6"/>
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
@@ -1653,7 +2233,7 @@
       <c r="K34" s="6"/>
       <c r="L34" s="6"/>
     </row>
-    <row r="35" spans="1:12" ht="42.6" customHeight="1">
+    <row r="35" spans="1:12" ht="42.65" customHeight="1">
       <c r="A35" s="6"/>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
@@ -1667,7 +2247,7 @@
       <c r="K35" s="6"/>
       <c r="L35" s="6"/>
     </row>
-    <row r="36" spans="1:12" ht="42.6" customHeight="1">
+    <row r="36" spans="1:12" ht="42.65" customHeight="1">
       <c r="A36" s="6"/>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -1681,7 +2261,7 @@
       <c r="K36" s="6"/>
       <c r="L36" s="6"/>
     </row>
-    <row r="37" spans="1:12" ht="42.6" customHeight="1">
+    <row r="37" spans="1:12" ht="42.65" customHeight="1">
       <c r="A37" s="6"/>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -1695,7 +2275,7 @@
       <c r="K37" s="6"/>
       <c r="L37" s="6"/>
     </row>
-    <row r="38" spans="1:12" ht="42.6" customHeight="1">
+    <row r="38" spans="1:12" ht="42.65" customHeight="1">
       <c r="A38" s="6"/>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
@@ -1709,7 +2289,7 @@
       <c r="K38" s="6"/>
       <c r="L38" s="6"/>
     </row>
-    <row r="39" spans="1:12" ht="42.6" customHeight="1">
+    <row r="39" spans="1:12" ht="42.65" customHeight="1">
       <c r="A39" s="6"/>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
@@ -1723,7 +2303,7 @@
       <c r="K39" s="6"/>
       <c r="L39" s="6"/>
     </row>
-    <row r="40" spans="1:12" ht="42.6" customHeight="1">
+    <row r="40" spans="1:12" ht="42.65" customHeight="1">
       <c r="A40" s="6"/>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
@@ -1737,7 +2317,7 @@
       <c r="K40" s="6"/>
       <c r="L40" s="6"/>
     </row>
-    <row r="41" spans="1:12" ht="42.6" customHeight="1">
+    <row r="41" spans="1:12" ht="42.65" customHeight="1">
       <c r="A41" s="6"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -1751,7 +2331,7 @@
       <c r="K41" s="6"/>
       <c r="L41" s="6"/>
     </row>
-    <row r="42" spans="1:12" ht="42.6" customHeight="1">
+    <row r="42" spans="1:12" ht="42.65" customHeight="1">
       <c r="A42" s="6"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
@@ -1765,7 +2345,7 @@
       <c r="K42" s="6"/>
       <c r="L42" s="6"/>
     </row>
-    <row r="43" spans="1:12" ht="42.6" customHeight="1">
+    <row r="43" spans="1:12" ht="42.65" customHeight="1">
       <c r="A43" s="6"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
@@ -1779,7 +2359,7 @@
       <c r="K43" s="6"/>
       <c r="L43" s="6"/>
     </row>
-    <row r="44" spans="1:12" ht="42.6" customHeight="1">
+    <row r="44" spans="1:12" ht="42.65" customHeight="1">
       <c r="A44" s="6"/>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
@@ -1793,7 +2373,7 @@
       <c r="K44" s="6"/>
       <c r="L44" s="6"/>
     </row>
-    <row r="45" spans="1:12" ht="42.6" customHeight="1">
+    <row r="45" spans="1:12" ht="42.65" customHeight="1">
       <c r="A45" s="6"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
@@ -1807,7 +2387,7 @@
       <c r="K45" s="6"/>
       <c r="L45" s="6"/>
     </row>
-    <row r="46" spans="1:12" ht="42.6" customHeight="1">
+    <row r="46" spans="1:12" ht="42.65" customHeight="1">
       <c r="A46" s="6"/>
       <c r="B46" s="6"/>
       <c r="C46" s="6"/>
@@ -1821,7 +2401,7 @@
       <c r="K46" s="6"/>
       <c r="L46" s="6"/>
     </row>
-    <row r="47" spans="1:12" ht="42.6" customHeight="1">
+    <row r="47" spans="1:12" ht="42.65" customHeight="1">
       <c r="A47" s="6"/>
       <c r="B47" s="6"/>
       <c r="C47" s="6"/>
@@ -1835,7 +2415,7 @@
       <c r="K47" s="6"/>
       <c r="L47" s="6"/>
     </row>
-    <row r="48" spans="1:12" ht="42.6" customHeight="1">
+    <row r="48" spans="1:12" ht="42.65" customHeight="1">
       <c r="A48" s="6"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
@@ -1849,7 +2429,7 @@
       <c r="K48" s="6"/>
       <c r="L48" s="6"/>
     </row>
-    <row r="49" spans="1:12" ht="42.6" customHeight="1">
+    <row r="49" spans="1:12" ht="42.65" customHeight="1">
       <c r="A49" s="6"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -1863,7 +2443,7 @@
       <c r="K49" s="6"/>
       <c r="L49" s="6"/>
     </row>
-    <row r="50" spans="1:12" ht="42.6" customHeight="1">
+    <row r="50" spans="1:12" ht="42.65" customHeight="1">
       <c r="A50" s="6"/>
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
@@ -1877,7 +2457,7 @@
       <c r="K50" s="6"/>
       <c r="L50" s="6"/>
     </row>
-    <row r="51" spans="1:12" ht="42.6" customHeight="1">
+    <row r="51" spans="1:12" ht="42.65" customHeight="1">
       <c r="A51" s="6"/>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
@@ -1891,7 +2471,7 @@
       <c r="K51" s="6"/>
       <c r="L51" s="6"/>
     </row>
-    <row r="52" spans="1:12" ht="42.6" customHeight="1">
+    <row r="52" spans="1:12" ht="42.65" customHeight="1">
       <c r="A52" s="6"/>
       <c r="B52" s="6"/>
       <c r="C52" s="6"/>
@@ -1905,7 +2485,7 @@
       <c r="K52" s="6"/>
       <c r="L52" s="6"/>
     </row>
-    <row r="53" spans="1:12" ht="42.6" customHeight="1">
+    <row r="53" spans="1:12" ht="42.65" customHeight="1">
       <c r="A53" s="6"/>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
@@ -1919,7 +2499,7 @@
       <c r="K53" s="6"/>
       <c r="L53" s="6"/>
     </row>
-    <row r="54" spans="1:12" ht="42.6" customHeight="1">
+    <row r="54" spans="1:12" ht="42.65" customHeight="1">
       <c r="A54" s="6"/>
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
@@ -1933,7 +2513,7 @@
       <c r="K54" s="6"/>
       <c r="L54" s="6"/>
     </row>
-    <row r="55" spans="1:12" ht="42.6" customHeight="1">
+    <row r="55" spans="1:12" ht="42.65" customHeight="1">
       <c r="A55" s="6"/>
       <c r="B55" s="6"/>
       <c r="C55" s="6"/>
@@ -1947,7 +2527,7 @@
       <c r="K55" s="6"/>
       <c r="L55" s="6"/>
     </row>
-    <row r="56" spans="1:12" ht="42.6" customHeight="1">
+    <row r="56" spans="1:12" ht="42.65" customHeight="1">
       <c r="A56" s="6"/>
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
@@ -1961,7 +2541,7 @@
       <c r="K56" s="6"/>
       <c r="L56" s="6"/>
     </row>
-    <row r="57" spans="1:12" ht="42.6" customHeight="1">
+    <row r="57" spans="1:12" ht="42.65" customHeight="1">
       <c r="A57" s="6"/>
       <c r="B57" s="6"/>
       <c r="C57" s="6"/>
@@ -1975,7 +2555,7 @@
       <c r="K57" s="6"/>
       <c r="L57" s="6"/>
     </row>
-    <row r="58" spans="1:12" ht="42.6" customHeight="1">
+    <row r="58" spans="1:12" ht="42.65" customHeight="1">
       <c r="A58" s="6"/>
       <c r="B58" s="6"/>
       <c r="C58" s="6"/>
@@ -1989,7 +2569,7 @@
       <c r="K58" s="6"/>
       <c r="L58" s="6"/>
     </row>
-    <row r="59" spans="1:12" ht="42.6" customHeight="1">
+    <row r="59" spans="1:12" ht="42.65" customHeight="1">
       <c r="A59" s="6"/>
       <c r="B59" s="6"/>
       <c r="C59" s="6"/>
@@ -2003,7 +2583,7 @@
       <c r="K59" s="6"/>
       <c r="L59" s="6"/>
     </row>
-    <row r="60" spans="1:12" ht="42.6" customHeight="1">
+    <row r="60" spans="1:12" ht="42.65" customHeight="1">
       <c r="A60" s="6"/>
       <c r="B60" s="6"/>
       <c r="C60" s="6"/>
@@ -2017,7 +2597,7 @@
       <c r="K60" s="6"/>
       <c r="L60" s="6"/>
     </row>
-    <row r="61" spans="1:12" ht="42.6" customHeight="1">
+    <row r="61" spans="1:12" ht="42.65" customHeight="1">
       <c r="A61" s="6"/>
       <c r="B61" s="6"/>
       <c r="C61" s="6"/>
@@ -2031,7 +2611,7 @@
       <c r="K61" s="6"/>
       <c r="L61" s="6"/>
     </row>
-    <row r="62" spans="1:12" ht="42.6" customHeight="1">
+    <row r="62" spans="1:12" ht="42.65" customHeight="1">
       <c r="A62" s="6"/>
       <c r="B62" s="6"/>
       <c r="C62" s="6"/>
@@ -2045,7 +2625,7 @@
       <c r="K62" s="6"/>
       <c r="L62" s="6"/>
     </row>
-    <row r="63" spans="1:12" ht="42.6" customHeight="1">
+    <row r="63" spans="1:12" ht="42.65" customHeight="1">
       <c r="A63" s="6"/>
       <c r="B63" s="6"/>
       <c r="C63" s="6"/>
@@ -2059,7 +2639,7 @@
       <c r="K63" s="6"/>
       <c r="L63" s="6"/>
     </row>
-    <row r="64" spans="1:12" ht="42.6" customHeight="1">
+    <row r="64" spans="1:12" ht="42.65" customHeight="1">
       <c r="A64" s="6"/>
       <c r="B64" s="6"/>
       <c r="C64" s="6"/>
@@ -2073,7 +2653,7 @@
       <c r="K64" s="6"/>
       <c r="L64" s="6"/>
     </row>
-    <row r="65" spans="1:12" ht="42.6" customHeight="1">
+    <row r="65" spans="1:12" ht="42.65" customHeight="1">
       <c r="A65" s="6"/>
       <c r="B65" s="6"/>
       <c r="C65" s="6"/>
@@ -2087,7 +2667,7 @@
       <c r="K65" s="6"/>
       <c r="L65" s="6"/>
     </row>
-    <row r="66" spans="1:12" ht="42.6" customHeight="1">
+    <row r="66" spans="1:12" ht="42.65" customHeight="1">
       <c r="A66" s="6"/>
       <c r="B66" s="6"/>
       <c r="C66" s="6"/>
@@ -2101,7 +2681,7 @@
       <c r="K66" s="6"/>
       <c r="L66" s="6"/>
     </row>
-    <row r="67" spans="1:12" ht="42.6" customHeight="1">
+    <row r="67" spans="1:12" ht="42.65" customHeight="1">
       <c r="A67" s="6"/>
       <c r="B67" s="6"/>
       <c r="C67" s="6"/>
@@ -2115,7 +2695,7 @@
       <c r="K67" s="6"/>
       <c r="L67" s="6"/>
     </row>
-    <row r="68" spans="1:12" ht="42.6" customHeight="1">
+    <row r="68" spans="1:12" ht="42.65" customHeight="1">
       <c r="A68" s="6"/>
       <c r="B68" s="6"/>
       <c r="C68" s="6"/>
@@ -2129,7 +2709,7 @@
       <c r="K68" s="6"/>
       <c r="L68" s="6"/>
     </row>
-    <row r="69" spans="1:12" ht="42.6" customHeight="1">
+    <row r="69" spans="1:12" ht="42.65" customHeight="1">
       <c r="A69" s="6"/>
       <c r="B69" s="6"/>
       <c r="C69" s="6"/>
@@ -2143,7 +2723,7 @@
       <c r="K69" s="6"/>
       <c r="L69" s="6"/>
     </row>
-    <row r="70" spans="1:12" ht="42.6" customHeight="1">
+    <row r="70" spans="1:12" ht="42.65" customHeight="1">
       <c r="A70" s="6"/>
       <c r="B70" s="6"/>
       <c r="C70" s="6"/>
@@ -2157,7 +2737,7 @@
       <c r="K70" s="6"/>
       <c r="L70" s="6"/>
     </row>
-    <row r="71" spans="1:12" ht="42.6" customHeight="1">
+    <row r="71" spans="1:12" ht="42.65" customHeight="1">
       <c r="A71" s="6"/>
       <c r="B71" s="6"/>
       <c r="C71" s="6"/>
@@ -2171,7 +2751,7 @@
       <c r="K71" s="6"/>
       <c r="L71" s="6"/>
     </row>
-    <row r="72" spans="1:12" ht="42.6" customHeight="1">
+    <row r="72" spans="1:12" ht="42.65" customHeight="1">
       <c r="A72" s="6"/>
       <c r="B72" s="6"/>
       <c r="C72" s="6"/>
@@ -2185,7 +2765,7 @@
       <c r="K72" s="6"/>
       <c r="L72" s="6"/>
     </row>
-    <row r="73" spans="1:12" ht="42.6" customHeight="1">
+    <row r="73" spans="1:12" ht="42.65" customHeight="1">
       <c r="A73" s="6"/>
       <c r="B73" s="6"/>
       <c r="C73" s="6"/>
@@ -2199,7 +2779,7 @@
       <c r="K73" s="6"/>
       <c r="L73" s="6"/>
     </row>
-    <row r="74" spans="1:12" ht="42.6" customHeight="1">
+    <row r="74" spans="1:12" ht="42.65" customHeight="1">
       <c r="A74" s="6"/>
       <c r="B74" s="6"/>
       <c r="C74" s="6"/>
@@ -2213,7 +2793,7 @@
       <c r="K74" s="6"/>
       <c r="L74" s="6"/>
     </row>
-    <row r="75" spans="1:12" ht="42.6" customHeight="1">
+    <row r="75" spans="1:12" ht="42.65" customHeight="1">
       <c r="A75" s="6"/>
       <c r="B75" s="6"/>
       <c r="C75" s="6"/>
@@ -2227,7 +2807,7 @@
       <c r="K75" s="6"/>
       <c r="L75" s="6"/>
     </row>
-    <row r="76" spans="1:12" ht="42.6" customHeight="1">
+    <row r="76" spans="1:12" ht="42.65" customHeight="1">
       <c r="A76" s="6"/>
       <c r="B76" s="6"/>
       <c r="C76" s="6"/>
@@ -2241,7 +2821,7 @@
       <c r="K76" s="6"/>
       <c r="L76" s="6"/>
     </row>
-    <row r="77" spans="1:12" ht="42.6" customHeight="1">
+    <row r="77" spans="1:12" ht="42.65" customHeight="1">
       <c r="A77" s="6"/>
       <c r="B77" s="6"/>
       <c r="C77" s="6"/>
@@ -2255,7 +2835,7 @@
       <c r="K77" s="6"/>
       <c r="L77" s="6"/>
     </row>
-    <row r="78" spans="1:12" ht="42.6" customHeight="1">
+    <row r="78" spans="1:12" ht="42.65" customHeight="1">
       <c r="A78" s="6"/>
       <c r="B78" s="6"/>
       <c r="C78" s="6"/>
@@ -2269,7 +2849,7 @@
       <c r="K78" s="6"/>
       <c r="L78" s="6"/>
     </row>
-    <row r="79" spans="1:12" ht="42.6" customHeight="1">
+    <row r="79" spans="1:12" ht="42.65" customHeight="1">
       <c r="A79" s="6"/>
       <c r="B79" s="6"/>
       <c r="C79" s="6"/>
@@ -2283,7 +2863,7 @@
       <c r="K79" s="6"/>
       <c r="L79" s="6"/>
     </row>
-    <row r="80" spans="1:12" ht="42.6" customHeight="1">
+    <row r="80" spans="1:12" ht="42.65" customHeight="1">
       <c r="A80" s="6"/>
       <c r="B80" s="6"/>
       <c r="C80" s="6"/>
@@ -2297,7 +2877,7 @@
       <c r="K80" s="6"/>
       <c r="L80" s="6"/>
     </row>
-    <row r="81" spans="1:12" ht="42.6" customHeight="1">
+    <row r="81" spans="1:12" ht="42.65" customHeight="1">
       <c r="A81" s="6"/>
       <c r="B81" s="6"/>
       <c r="C81" s="6"/>
@@ -2311,7 +2891,7 @@
       <c r="K81" s="6"/>
       <c r="L81" s="6"/>
     </row>
-    <row r="82" spans="1:12" ht="42.6" customHeight="1">
+    <row r="82" spans="1:12" ht="42.65" customHeight="1">
       <c r="A82" s="6"/>
       <c r="B82" s="6"/>
       <c r="C82" s="6"/>
@@ -2325,7 +2905,7 @@
       <c r="K82" s="6"/>
       <c r="L82" s="6"/>
     </row>
-    <row r="83" spans="1:12" ht="42.6" customHeight="1">
+    <row r="83" spans="1:12" ht="42.65" customHeight="1">
       <c r="A83" s="6"/>
       <c r="B83" s="6"/>
       <c r="C83" s="6"/>
@@ -2339,7 +2919,7 @@
       <c r="K83" s="6"/>
       <c r="L83" s="6"/>
     </row>
-    <row r="84" spans="1:12" ht="42.6" customHeight="1">
+    <row r="84" spans="1:12" ht="42.65" customHeight="1">
       <c r="A84" s="6"/>
       <c r="B84" s="6"/>
       <c r="C84" s="6"/>
@@ -2353,7 +2933,7 @@
       <c r="K84" s="6"/>
       <c r="L84" s="6"/>
     </row>
-    <row r="85" spans="1:12" ht="42.6" customHeight="1">
+    <row r="85" spans="1:12" ht="42.65" customHeight="1">
       <c r="A85" s="6"/>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
@@ -2367,7 +2947,7 @@
       <c r="K85" s="6"/>
       <c r="L85" s="6"/>
     </row>
-    <row r="86" spans="1:12" ht="42.6" customHeight="1">
+    <row r="86" spans="1:12" ht="42.65" customHeight="1">
       <c r="A86" s="6"/>
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
@@ -2381,7 +2961,7 @@
       <c r="K86" s="6"/>
       <c r="L86" s="6"/>
     </row>
-    <row r="87" spans="1:12" ht="42.6" customHeight="1">
+    <row r="87" spans="1:12" ht="42.65" customHeight="1">
       <c r="A87" s="6"/>
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
@@ -2395,7 +2975,7 @@
       <c r="K87" s="6"/>
       <c r="L87" s="6"/>
     </row>
-    <row r="88" spans="1:12" ht="42.6" customHeight="1">
+    <row r="88" spans="1:12" ht="42.65" customHeight="1">
       <c r="A88" s="6"/>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
@@ -2409,7 +2989,7 @@
       <c r="K88" s="6"/>
       <c r="L88" s="6"/>
     </row>
-    <row r="89" spans="1:12" ht="42.6" customHeight="1">
+    <row r="89" spans="1:12" ht="42.65" customHeight="1">
       <c r="A89" s="6"/>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
@@ -2423,7 +3003,7 @@
       <c r="K89" s="6"/>
       <c r="L89" s="6"/>
     </row>
-    <row r="90" spans="1:12" ht="42.6" customHeight="1">
+    <row r="90" spans="1:12" ht="42.65" customHeight="1">
       <c r="A90" s="6"/>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
@@ -2437,7 +3017,7 @@
       <c r="K90" s="6"/>
       <c r="L90" s="6"/>
     </row>
-    <row r="91" spans="1:12" ht="42.6" customHeight="1">
+    <row r="91" spans="1:12" ht="42.65" customHeight="1">
       <c r="A91" s="6"/>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
@@ -2451,7 +3031,7 @@
       <c r="K91" s="6"/>
       <c r="L91" s="6"/>
     </row>
-    <row r="92" spans="1:12" ht="42.6" customHeight="1">
+    <row r="92" spans="1:12" ht="42.65" customHeight="1">
       <c r="A92" s="6"/>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
@@ -2465,7 +3045,7 @@
       <c r="K92" s="6"/>
       <c r="L92" s="6"/>
     </row>
-    <row r="93" spans="1:12" ht="42.6" customHeight="1">
+    <row r="93" spans="1:12" ht="42.65" customHeight="1">
       <c r="A93" s="6"/>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -2479,7 +3059,7 @@
       <c r="K93" s="6"/>
       <c r="L93" s="6"/>
     </row>
-    <row r="94" spans="1:12" ht="42.6" customHeight="1">
+    <row r="94" spans="1:12" ht="42.65" customHeight="1">
       <c r="A94" s="6"/>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -2493,7 +3073,7 @@
       <c r="K94" s="6"/>
       <c r="L94" s="6"/>
     </row>
-    <row r="95" spans="1:12" ht="42.6" customHeight="1">
+    <row r="95" spans="1:12" ht="42.65" customHeight="1">
       <c r="A95" s="6"/>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -2507,7 +3087,7 @@
       <c r="K95" s="6"/>
       <c r="L95" s="6"/>
     </row>
-    <row r="96" spans="1:12" ht="42.6" customHeight="1">
+    <row r="96" spans="1:12" ht="42.65" customHeight="1">
       <c r="A96" s="6"/>
       <c r="B96" s="6"/>
       <c r="C96" s="6"/>
@@ -2521,7 +3101,7 @@
       <c r="K96" s="6"/>
       <c r="L96" s="6"/>
     </row>
-    <row r="97" spans="1:12" ht="42.6" customHeight="1">
+    <row r="97" spans="1:12" ht="42.65" customHeight="1">
       <c r="A97" s="6"/>
       <c r="B97" s="6"/>
       <c r="C97" s="6"/>
@@ -2535,7 +3115,7 @@
       <c r="K97" s="6"/>
       <c r="L97" s="6"/>
     </row>
-    <row r="98" spans="1:12" ht="42.6" customHeight="1">
+    <row r="98" spans="1:12" ht="42.65" customHeight="1">
       <c r="A98" s="6"/>
       <c r="B98" s="6"/>
       <c r="C98" s="6"/>
@@ -2549,7 +3129,7 @@
       <c r="K98" s="6"/>
       <c r="L98" s="6"/>
     </row>
-    <row r="99" spans="1:12" ht="42.6" customHeight="1">
+    <row r="99" spans="1:12" ht="42.65" customHeight="1">
       <c r="A99" s="6"/>
       <c r="B99" s="6"/>
       <c r="C99" s="6"/>
@@ -2563,7 +3143,7 @@
       <c r="K99" s="6"/>
       <c r="L99" s="6"/>
     </row>
-    <row r="100" spans="1:12" ht="42.6" customHeight="1">
+    <row r="100" spans="1:12" ht="42.65" customHeight="1">
       <c r="A100" s="6"/>
       <c r="B100" s="6"/>
       <c r="C100" s="6"/>
@@ -2577,7 +3157,7 @@
       <c r="K100" s="6"/>
       <c r="L100" s="6"/>
     </row>
-    <row r="101" spans="1:12" ht="42.6" customHeight="1">
+    <row r="101" spans="1:12" ht="42.65" customHeight="1">
       <c r="A101" s="6"/>
       <c r="B101" s="6"/>
       <c r="C101" s="6"/>
@@ -2591,7 +3171,7 @@
       <c r="K101" s="6"/>
       <c r="L101" s="6"/>
     </row>
-    <row r="102" spans="1:12" ht="42.6" customHeight="1">
+    <row r="102" spans="1:12" ht="42.65" customHeight="1">
       <c r="A102" s="6"/>
       <c r="B102" s="6"/>
       <c r="C102" s="6"/>
@@ -2605,7 +3185,7 @@
       <c r="K102" s="6"/>
       <c r="L102" s="6"/>
     </row>
-    <row r="103" spans="1:12" ht="42.6" customHeight="1">
+    <row r="103" spans="1:12" ht="42.65" customHeight="1">
       <c r="A103" s="6"/>
       <c r="B103" s="6"/>
       <c r="C103" s="6"/>
@@ -2619,7 +3199,7 @@
       <c r="K103" s="6"/>
       <c r="L103" s="6"/>
     </row>
-    <row r="104" spans="1:12" ht="42.6" customHeight="1">
+    <row r="104" spans="1:12" ht="42.65" customHeight="1">
       <c r="A104" s="6"/>
       <c r="B104" s="6"/>
       <c r="C104" s="6"/>
@@ -2633,7 +3213,7 @@
       <c r="K104" s="6"/>
       <c r="L104" s="6"/>
     </row>
-    <row r="105" spans="1:12" ht="42.6" customHeight="1">
+    <row r="105" spans="1:12" ht="42.65" customHeight="1">
       <c r="A105" s="6"/>
       <c r="B105" s="6"/>
       <c r="C105" s="6"/>
@@ -2647,7 +3227,7 @@
       <c r="K105" s="6"/>
       <c r="L105" s="6"/>
     </row>
-    <row r="106" spans="1:12" ht="42.6" customHeight="1">
+    <row r="106" spans="1:12" ht="42.65" customHeight="1">
       <c r="A106" s="6"/>
       <c r="B106" s="6"/>
       <c r="C106" s="6"/>
@@ -2661,7 +3241,7 @@
       <c r="K106" s="6"/>
       <c r="L106" s="6"/>
     </row>
-    <row r="107" spans="1:12" ht="42.6" customHeight="1">
+    <row r="107" spans="1:12" ht="42.65" customHeight="1">
       <c r="A107" s="6"/>
       <c r="B107" s="6"/>
       <c r="C107" s="6"/>
@@ -2675,7 +3255,7 @@
       <c r="K107" s="6"/>
       <c r="L107" s="6"/>
     </row>
-    <row r="108" spans="1:12" ht="42.6" customHeight="1">
+    <row r="108" spans="1:12" ht="42.65" customHeight="1">
       <c r="A108" s="6"/>
       <c r="B108" s="6"/>
       <c r="C108" s="6"/>
@@ -2689,7 +3269,7 @@
       <c r="K108" s="6"/>
       <c r="L108" s="6"/>
     </row>
-    <row r="109" spans="1:12" ht="42.6" customHeight="1">
+    <row r="109" spans="1:12" ht="42.65" customHeight="1">
       <c r="A109" s="6"/>
       <c r="B109" s="6"/>
       <c r="C109" s="6"/>
@@ -2703,7 +3283,7 @@
       <c r="K109" s="6"/>
       <c r="L109" s="6"/>
     </row>
-    <row r="110" spans="1:12" ht="42.6" customHeight="1">
+    <row r="110" spans="1:12" ht="42.65" customHeight="1">
       <c r="A110" s="6"/>
       <c r="B110" s="6"/>
       <c r="C110" s="6"/>
@@ -2717,7 +3297,7 @@
       <c r="K110" s="6"/>
       <c r="L110" s="6"/>
     </row>
-    <row r="111" spans="1:12" ht="42.6" customHeight="1">
+    <row r="111" spans="1:12" ht="42.65" customHeight="1">
       <c r="A111" s="6"/>
       <c r="B111" s="6"/>
       <c r="C111" s="6"/>
@@ -2731,7 +3311,7 @@
       <c r="K111" s="6"/>
       <c r="L111" s="6"/>
     </row>
-    <row r="112" spans="1:12" ht="42.6" customHeight="1">
+    <row r="112" spans="1:12" ht="42.65" customHeight="1">
       <c r="A112" s="6"/>
       <c r="B112" s="6"/>
       <c r="C112" s="6"/>
@@ -2745,7 +3325,7 @@
       <c r="K112" s="6"/>
       <c r="L112" s="6"/>
     </row>
-    <row r="113" spans="1:12" ht="42.6" customHeight="1">
+    <row r="113" spans="1:12" ht="42.65" customHeight="1">
       <c r="A113" s="6"/>
       <c r="B113" s="6"/>
       <c r="C113" s="6"/>
@@ -2759,7 +3339,7 @@
       <c r="K113" s="6"/>
       <c r="L113" s="6"/>
     </row>
-    <row r="114" spans="1:12" ht="42.6" customHeight="1">
+    <row r="114" spans="1:12" ht="42.65" customHeight="1">
       <c r="A114" s="6"/>
       <c r="B114" s="6"/>
       <c r="C114" s="6"/>
@@ -2773,7 +3353,7 @@
       <c r="K114" s="6"/>
       <c r="L114" s="6"/>
     </row>
-    <row r="115" spans="1:12" ht="42.6" customHeight="1">
+    <row r="115" spans="1:12" ht="42.65" customHeight="1">
       <c r="A115" s="6"/>
       <c r="B115" s="6"/>
       <c r="C115" s="6"/>
@@ -2787,7 +3367,7 @@
       <c r="K115" s="6"/>
       <c r="L115" s="6"/>
     </row>
-    <row r="116" spans="1:12" ht="42.6" customHeight="1">
+    <row r="116" spans="1:12" ht="42.65" customHeight="1">
       <c r="A116" s="6"/>
       <c r="B116" s="6"/>
       <c r="C116" s="6"/>
@@ -2801,7 +3381,7 @@
       <c r="K116" s="6"/>
       <c r="L116" s="6"/>
     </row>
-    <row r="117" spans="1:12" ht="42.6" customHeight="1">
+    <row r="117" spans="1:12" ht="42.65" customHeight="1">
       <c r="A117" s="6"/>
       <c r="B117" s="6"/>
       <c r="C117" s="6"/>
@@ -2815,7 +3395,7 @@
       <c r="K117" s="6"/>
       <c r="L117" s="6"/>
     </row>
-    <row r="118" spans="1:12" ht="42.6" customHeight="1">
+    <row r="118" spans="1:12" ht="42.65" customHeight="1">
       <c r="A118" s="6"/>
       <c r="B118" s="6"/>
       <c r="C118" s="6"/>
@@ -2829,7 +3409,7 @@
       <c r="K118" s="6"/>
       <c r="L118" s="6"/>
     </row>
-    <row r="119" spans="1:12" ht="42.6" customHeight="1">
+    <row r="119" spans="1:12" ht="42.65" customHeight="1">
       <c r="A119" s="6"/>
       <c r="B119" s="6"/>
       <c r="C119" s="6"/>
@@ -2843,7 +3423,7 @@
       <c r="K119" s="6"/>
       <c r="L119" s="6"/>
     </row>
-    <row r="120" spans="1:12" ht="42.6" customHeight="1">
+    <row r="120" spans="1:12" ht="42.65" customHeight="1">
       <c r="A120" s="6"/>
       <c r="B120" s="6"/>
       <c r="C120" s="6"/>
@@ -2857,7 +3437,7 @@
       <c r="K120" s="6"/>
       <c r="L120" s="6"/>
     </row>
-    <row r="121" spans="1:12" ht="42.6" customHeight="1">
+    <row r="121" spans="1:12" ht="42.65" customHeight="1">
       <c r="A121" s="6"/>
       <c r="B121" s="6"/>
       <c r="C121" s="6"/>
@@ -2871,7 +3451,7 @@
       <c r="K121" s="6"/>
       <c r="L121" s="6"/>
     </row>
-    <row r="122" spans="1:12" ht="42.6" customHeight="1">
+    <row r="122" spans="1:12" ht="42.65" customHeight="1">
       <c r="A122" s="6"/>
       <c r="B122" s="6"/>
       <c r="C122" s="6"/>
@@ -2885,7 +3465,7 @@
       <c r="K122" s="6"/>
       <c r="L122" s="6"/>
     </row>
-    <row r="123" spans="1:12" ht="42.6" customHeight="1">
+    <row r="123" spans="1:12" ht="42.65" customHeight="1">
       <c r="A123" s="6"/>
       <c r="B123" s="6"/>
       <c r="C123" s="6"/>
@@ -2899,7 +3479,7 @@
       <c r="K123" s="6"/>
       <c r="L123" s="6"/>
     </row>
-    <row r="124" spans="1:12" ht="42.6" customHeight="1">
+    <row r="124" spans="1:12" ht="42.65" customHeight="1">
       <c r="A124" s="6"/>
       <c r="B124" s="6"/>
       <c r="C124" s="6"/>
@@ -2913,7 +3493,7 @@
       <c r="K124" s="6"/>
       <c r="L124" s="6"/>
     </row>
-    <row r="125" spans="1:12" ht="42.6" customHeight="1">
+    <row r="125" spans="1:12" ht="42.65" customHeight="1">
       <c r="A125" s="6"/>
       <c r="B125" s="6"/>
       <c r="C125" s="6"/>
@@ -2927,7 +3507,7 @@
       <c r="K125" s="6"/>
       <c r="L125" s="6"/>
     </row>
-    <row r="126" spans="1:12" ht="42.6" customHeight="1">
+    <row r="126" spans="1:12" ht="42.65" customHeight="1">
       <c r="A126" s="6"/>
       <c r="B126" s="6"/>
       <c r="C126" s="6"/>
@@ -2941,7 +3521,7 @@
       <c r="K126" s="6"/>
       <c r="L126" s="6"/>
     </row>
-    <row r="127" spans="1:12" ht="42.6" customHeight="1">
+    <row r="127" spans="1:12" ht="42.65" customHeight="1">
       <c r="A127" s="6"/>
       <c r="B127" s="6"/>
       <c r="C127" s="6"/>
@@ -2955,7 +3535,7 @@
       <c r="K127" s="6"/>
       <c r="L127" s="6"/>
     </row>
-    <row r="128" spans="1:12" ht="42.6" customHeight="1">
+    <row r="128" spans="1:12" ht="42.65" customHeight="1">
       <c r="A128" s="6"/>
       <c r="B128" s="6"/>
       <c r="C128" s="6"/>
@@ -2969,7 +3549,7 @@
       <c r="K128" s="6"/>
       <c r="L128" s="6"/>
     </row>
-    <row r="129" spans="1:12" ht="42.6" customHeight="1">
+    <row r="129" spans="1:12" ht="42.65" customHeight="1">
       <c r="A129" s="6"/>
       <c r="B129" s="6"/>
       <c r="C129" s="6"/>
@@ -2983,7 +3563,7 @@
       <c r="K129" s="6"/>
       <c r="L129" s="6"/>
     </row>
-    <row r="130" spans="1:12" ht="42.6" customHeight="1">
+    <row r="130" spans="1:12" ht="42.65" customHeight="1">
       <c r="A130" s="6"/>
       <c r="B130" s="6"/>
       <c r="C130" s="6"/>
@@ -2997,7 +3577,7 @@
       <c r="K130" s="6"/>
       <c r="L130" s="6"/>
     </row>
-    <row r="131" spans="1:12" ht="42.6" customHeight="1">
+    <row r="131" spans="1:12" ht="42.65" customHeight="1">
       <c r="A131" s="6"/>
       <c r="B131" s="6"/>
       <c r="C131" s="6"/>
@@ -3011,7 +3591,7 @@
       <c r="K131" s="6"/>
       <c r="L131" s="6"/>
     </row>
-    <row r="132" spans="1:12" ht="42.6" customHeight="1">
+    <row r="132" spans="1:12" ht="42.65" customHeight="1">
       <c r="A132" s="6"/>
       <c r="B132" s="6"/>
       <c r="C132" s="6"/>
@@ -3025,7 +3605,7 @@
       <c r="K132" s="6"/>
       <c r="L132" s="6"/>
     </row>
-    <row r="133" spans="1:12" ht="42.6" customHeight="1">
+    <row r="133" spans="1:12" ht="42.65" customHeight="1">
       <c r="A133" s="6"/>
       <c r="B133" s="6"/>
       <c r="C133" s="6"/>
@@ -3039,7 +3619,7 @@
       <c r="K133" s="6"/>
       <c r="L133" s="6"/>
     </row>
-    <row r="134" spans="1:12" ht="42.6" customHeight="1">
+    <row r="134" spans="1:12" ht="42.65" customHeight="1">
       <c r="A134" s="6"/>
       <c r="B134" s="6"/>
       <c r="C134" s="6"/>
@@ -3053,7 +3633,7 @@
       <c r="K134" s="6"/>
       <c r="L134" s="6"/>
     </row>
-    <row r="135" spans="1:12" ht="42.6" customHeight="1">
+    <row r="135" spans="1:12" ht="42.65" customHeight="1">
       <c r="A135" s="6"/>
       <c r="B135" s="6"/>
       <c r="C135" s="6"/>
@@ -3067,7 +3647,7 @@
       <c r="K135" s="6"/>
       <c r="L135" s="6"/>
     </row>
-    <row r="136" spans="1:12" ht="42.6" customHeight="1">
+    <row r="136" spans="1:12" ht="42.65" customHeight="1">
       <c r="A136" s="6"/>
       <c r="B136" s="6"/>
       <c r="C136" s="6"/>
@@ -3081,7 +3661,7 @@
       <c r="K136" s="6"/>
       <c r="L136" s="6"/>
     </row>
-    <row r="137" spans="1:12" ht="42.6" customHeight="1">
+    <row r="137" spans="1:12" ht="42.65" customHeight="1">
       <c r="A137" s="6"/>
       <c r="B137" s="6"/>
       <c r="C137" s="6"/>
@@ -3095,7 +3675,7 @@
       <c r="K137" s="6"/>
       <c r="L137" s="6"/>
     </row>
-    <row r="138" spans="1:12" ht="42.6" customHeight="1">
+    <row r="138" spans="1:12" ht="42.65" customHeight="1">
       <c r="A138" s="6"/>
       <c r="B138" s="6"/>
       <c r="C138" s="6"/>
@@ -3109,7 +3689,7 @@
       <c r="K138" s="6"/>
       <c r="L138" s="6"/>
     </row>
-    <row r="139" spans="1:12" ht="42.6" customHeight="1">
+    <row r="139" spans="1:12" ht="42.65" customHeight="1">
       <c r="A139" s="6"/>
       <c r="B139" s="6"/>
       <c r="C139" s="6"/>
@@ -3123,7 +3703,7 @@
       <c r="K139" s="6"/>
       <c r="L139" s="6"/>
     </row>
-    <row r="140" spans="1:12" ht="42.6" customHeight="1">
+    <row r="140" spans="1:12" ht="42.65" customHeight="1">
       <c r="A140" s="6"/>
       <c r="B140" s="6"/>
       <c r="C140" s="6"/>
@@ -3137,7 +3717,7 @@
       <c r="K140" s="6"/>
       <c r="L140" s="6"/>
     </row>
-    <row r="141" spans="1:12" ht="42.6" customHeight="1">
+    <row r="141" spans="1:12" ht="42.65" customHeight="1">
       <c r="A141" s="6"/>
       <c r="B141" s="6"/>
       <c r="C141" s="6"/>
@@ -3151,7 +3731,7 @@
       <c r="K141" s="6"/>
       <c r="L141" s="6"/>
     </row>
-    <row r="142" spans="1:12" ht="42.6" customHeight="1">
+    <row r="142" spans="1:12" ht="42.65" customHeight="1">
       <c r="A142" s="6"/>
       <c r="B142" s="6"/>
       <c r="C142" s="6"/>
@@ -3165,7 +3745,7 @@
       <c r="K142" s="6"/>
       <c r="L142" s="6"/>
     </row>
-    <row r="143" spans="1:12" ht="42.6" customHeight="1">
+    <row r="143" spans="1:12" ht="42.65" customHeight="1">
       <c r="A143" s="6"/>
       <c r="B143" s="6"/>
       <c r="C143" s="6"/>
@@ -3179,7 +3759,7 @@
       <c r="K143" s="6"/>
       <c r="L143" s="6"/>
     </row>
-    <row r="144" spans="1:12" ht="42.6" customHeight="1">
+    <row r="144" spans="1:12" ht="42.65" customHeight="1">
       <c r="A144" s="6"/>
       <c r="B144" s="6"/>
       <c r="C144" s="6"/>
@@ -3193,7 +3773,7 @@
       <c r="K144" s="6"/>
       <c r="L144" s="6"/>
     </row>
-    <row r="145" spans="1:12" ht="42.6" customHeight="1">
+    <row r="145" spans="1:12" ht="42.65" customHeight="1">
       <c r="A145" s="6"/>
       <c r="B145" s="6"/>
       <c r="C145" s="6"/>
@@ -3207,7 +3787,7 @@
       <c r="K145" s="6"/>
       <c r="L145" s="6"/>
     </row>
-    <row r="146" spans="1:12" ht="42.6" customHeight="1">
+    <row r="146" spans="1:12" ht="42.65" customHeight="1">
       <c r="A146" s="6"/>
       <c r="B146" s="6"/>
       <c r="C146" s="6"/>
@@ -3221,7 +3801,7 @@
       <c r="K146" s="6"/>
       <c r="L146" s="6"/>
     </row>
-    <row r="147" spans="1:12" ht="42.6" customHeight="1">
+    <row r="147" spans="1:12" ht="42.65" customHeight="1">
       <c r="A147" s="6"/>
       <c r="B147" s="6"/>
       <c r="C147" s="6"/>
@@ -3235,7 +3815,7 @@
       <c r="K147" s="6"/>
       <c r="L147" s="6"/>
     </row>
-    <row r="148" spans="1:12" ht="42.6" customHeight="1">
+    <row r="148" spans="1:12" ht="42.65" customHeight="1">
       <c r="A148" s="6"/>
       <c r="B148" s="6"/>
       <c r="C148" s="6"/>
@@ -3249,7 +3829,7 @@
       <c r="K148" s="6"/>
       <c r="L148" s="6"/>
     </row>
-    <row r="149" spans="1:12" ht="42.6" customHeight="1">
+    <row r="149" spans="1:12" ht="42.65" customHeight="1">
       <c r="A149" s="6"/>
       <c r="B149" s="6"/>
       <c r="C149" s="6"/>
@@ -3263,7 +3843,7 @@
       <c r="K149" s="6"/>
       <c r="L149" s="6"/>
     </row>
-    <row r="150" spans="1:12" ht="42.6" customHeight="1">
+    <row r="150" spans="1:12" ht="42.65" customHeight="1">
       <c r="A150" s="6"/>
       <c r="B150" s="6"/>
       <c r="C150" s="6"/>
@@ -3277,7 +3857,7 @@
       <c r="K150" s="6"/>
       <c r="L150" s="6"/>
     </row>
-    <row r="151" spans="1:12" ht="42.6" customHeight="1">
+    <row r="151" spans="1:12" ht="42.65" customHeight="1">
       <c r="A151" s="6"/>
       <c r="B151" s="6"/>
       <c r="C151" s="6"/>
@@ -3291,7 +3871,7 @@
       <c r="K151" s="6"/>
       <c r="L151" s="6"/>
     </row>
-    <row r="152" spans="1:12" ht="42.6" customHeight="1">
+    <row r="152" spans="1:12" ht="42.65" customHeight="1">
       <c r="A152" s="6"/>
       <c r="B152" s="6"/>
       <c r="C152" s="6"/>
@@ -3305,7 +3885,7 @@
       <c r="K152" s="6"/>
       <c r="L152" s="6"/>
     </row>
-    <row r="153" spans="1:12" ht="42.6" customHeight="1">
+    <row r="153" spans="1:12" ht="42.65" customHeight="1">
       <c r="A153" s="6"/>
       <c r="B153" s="6"/>
       <c r="C153" s="6"/>
@@ -3319,7 +3899,7 @@
       <c r="K153" s="6"/>
       <c r="L153" s="6"/>
     </row>
-    <row r="154" spans="1:12" ht="42.6" customHeight="1">
+    <row r="154" spans="1:12" ht="42.65" customHeight="1">
       <c r="A154" s="6"/>
       <c r="B154" s="6"/>
       <c r="C154" s="6"/>
@@ -3333,7 +3913,7 @@
       <c r="K154" s="6"/>
       <c r="L154" s="6"/>
     </row>
-    <row r="155" spans="1:12" ht="42.6" customHeight="1">
+    <row r="155" spans="1:12" ht="42.65" customHeight="1">
       <c r="A155" s="6"/>
       <c r="B155" s="6"/>
       <c r="C155" s="6"/>
@@ -3347,7 +3927,7 @@
       <c r="K155" s="6"/>
       <c r="L155" s="6"/>
     </row>
-    <row r="156" spans="1:12" ht="42.6" customHeight="1">
+    <row r="156" spans="1:12" ht="42.65" customHeight="1">
       <c r="A156" s="6"/>
       <c r="B156" s="6"/>
       <c r="C156" s="6"/>
@@ -3361,7 +3941,7 @@
       <c r="K156" s="6"/>
       <c r="L156" s="6"/>
     </row>
-    <row r="157" spans="1:12" ht="42.6" customHeight="1">
+    <row r="157" spans="1:12" ht="42.65" customHeight="1">
       <c r="A157" s="6"/>
       <c r="B157" s="6"/>
       <c r="C157" s="6"/>
@@ -3375,7 +3955,7 @@
       <c r="K157" s="6"/>
       <c r="L157" s="6"/>
     </row>
-    <row r="158" spans="1:12" ht="42.6" customHeight="1">
+    <row r="158" spans="1:12" ht="42.65" customHeight="1">
       <c r="A158" s="6"/>
       <c r="B158" s="6"/>
       <c r="C158" s="6"/>
@@ -3389,7 +3969,7 @@
       <c r="K158" s="6"/>
       <c r="L158" s="6"/>
     </row>
-    <row r="159" spans="1:12" ht="42.6" customHeight="1">
+    <row r="159" spans="1:12" ht="42.65" customHeight="1">
       <c r="A159" s="6"/>
       <c r="B159" s="6"/>
       <c r="C159" s="6"/>
@@ -3403,7 +3983,7 @@
       <c r="K159" s="6"/>
       <c r="L159" s="6"/>
     </row>
-    <row r="160" spans="1:12" ht="42.6" customHeight="1">
+    <row r="160" spans="1:12" ht="42.65" customHeight="1">
       <c r="A160" s="6"/>
       <c r="B160" s="6"/>
       <c r="C160" s="6"/>
@@ -3417,7 +3997,7 @@
       <c r="K160" s="6"/>
       <c r="L160" s="6"/>
     </row>
-    <row r="161" spans="1:12" ht="42.6" customHeight="1">
+    <row r="161" spans="1:12" ht="42.65" customHeight="1">
       <c r="A161" s="6"/>
       <c r="B161" s="6"/>
       <c r="C161" s="6"/>
@@ -3431,7 +4011,7 @@
       <c r="K161" s="6"/>
       <c r="L161" s="6"/>
     </row>
-    <row r="162" spans="1:12" ht="42.6" customHeight="1">
+    <row r="162" spans="1:12" ht="42.65" customHeight="1">
       <c r="A162" s="6"/>
       <c r="B162" s="6"/>
       <c r="C162" s="6"/>
@@ -3445,7 +4025,7 @@
       <c r="K162" s="6"/>
       <c r="L162" s="6"/>
     </row>
-    <row r="163" spans="1:12" ht="42.6" customHeight="1">
+    <row r="163" spans="1:12" ht="42.65" customHeight="1">
       <c r="A163" s="6"/>
       <c r="B163" s="6"/>
       <c r="C163" s="6"/>
@@ -3459,7 +4039,7 @@
       <c r="K163" s="6"/>
       <c r="L163" s="6"/>
     </row>
-    <row r="164" spans="1:12" ht="42.6" customHeight="1">
+    <row r="164" spans="1:12" ht="42.65" customHeight="1">
       <c r="A164" s="6"/>
       <c r="B164" s="6"/>
       <c r="C164" s="6"/>
@@ -3473,7 +4053,7 @@
       <c r="K164" s="6"/>
       <c r="L164" s="6"/>
     </row>
-    <row r="165" spans="1:12" ht="42.6" customHeight="1">
+    <row r="165" spans="1:12" ht="42.65" customHeight="1">
       <c r="A165" s="6"/>
       <c r="B165" s="6"/>
       <c r="C165" s="6"/>
@@ -3487,7 +4067,7 @@
       <c r="K165" s="6"/>
       <c r="L165" s="6"/>
     </row>
-    <row r="166" spans="1:12" ht="42.6" customHeight="1">
+    <row r="166" spans="1:12" ht="42.65" customHeight="1">
       <c r="A166" s="6"/>
       <c r="B166" s="6"/>
       <c r="C166" s="6"/>
@@ -3501,7 +4081,7 @@
       <c r="K166" s="6"/>
       <c r="L166" s="6"/>
     </row>
-    <row r="167" spans="1:12" ht="42.6" customHeight="1">
+    <row r="167" spans="1:12" ht="42.65" customHeight="1">
       <c r="A167" s="6"/>
       <c r="B167" s="6"/>
       <c r="C167" s="6"/>
@@ -3515,7 +4095,7 @@
       <c r="K167" s="6"/>
       <c r="L167" s="6"/>
     </row>
-    <row r="168" spans="1:12" ht="42.6" customHeight="1">
+    <row r="168" spans="1:12" ht="42.65" customHeight="1">
       <c r="A168" s="6"/>
       <c r="B168" s="6"/>
       <c r="C168" s="6"/>
@@ -3529,7 +4109,7 @@
       <c r="K168" s="6"/>
       <c r="L168" s="6"/>
     </row>
-    <row r="169" spans="1:12" ht="42.6" customHeight="1">
+    <row r="169" spans="1:12" ht="42.65" customHeight="1">
       <c r="A169" s="6"/>
       <c r="B169" s="6"/>
       <c r="C169" s="6"/>
@@ -3543,7 +4123,7 @@
       <c r="K169" s="6"/>
       <c r="L169" s="6"/>
     </row>
-    <row r="170" spans="1:12" ht="42.6" customHeight="1">
+    <row r="170" spans="1:12" ht="42.65" customHeight="1">
       <c r="A170" s="6"/>
       <c r="B170" s="6"/>
       <c r="C170" s="6"/>
@@ -3557,7 +4137,7 @@
       <c r="K170" s="6"/>
       <c r="L170" s="6"/>
     </row>
-    <row r="171" spans="1:12" ht="42.6" customHeight="1">
+    <row r="171" spans="1:12" ht="42.65" customHeight="1">
       <c r="A171" s="6"/>
       <c r="B171" s="6"/>
       <c r="C171" s="6"/>
@@ -3571,7 +4151,7 @@
       <c r="K171" s="6"/>
       <c r="L171" s="6"/>
     </row>
-    <row r="172" spans="1:12" ht="42.6" customHeight="1">
+    <row r="172" spans="1:12" ht="42.65" customHeight="1">
       <c r="A172" s="6"/>
       <c r="B172" s="6"/>
       <c r="C172" s="6"/>
@@ -3585,7 +4165,7 @@
       <c r="K172" s="6"/>
       <c r="L172" s="6"/>
     </row>
-    <row r="173" spans="1:12" ht="42.6" customHeight="1">
+    <row r="173" spans="1:12" ht="42.65" customHeight="1">
       <c r="A173" s="6"/>
       <c r="B173" s="6"/>
       <c r="C173" s="6"/>
@@ -3599,7 +4179,7 @@
       <c r="K173" s="6"/>
       <c r="L173" s="6"/>
     </row>
-    <row r="174" spans="1:12" ht="42.6" customHeight="1">
+    <row r="174" spans="1:12" ht="42.65" customHeight="1">
       <c r="A174" s="6"/>
       <c r="B174" s="6"/>
       <c r="C174" s="6"/>
@@ -3613,7 +4193,7 @@
       <c r="K174" s="6"/>
       <c r="L174" s="6"/>
     </row>
-    <row r="175" spans="1:12" ht="42.6" customHeight="1">
+    <row r="175" spans="1:12" ht="42.65" customHeight="1">
       <c r="A175" s="6"/>
       <c r="B175" s="6"/>
       <c r="C175" s="6"/>
@@ -3627,7 +4207,7 @@
       <c r="K175" s="6"/>
       <c r="L175" s="6"/>
     </row>
-    <row r="176" spans="1:12" ht="42.6" customHeight="1">
+    <row r="176" spans="1:12" ht="42.65" customHeight="1">
       <c r="A176" s="6"/>
       <c r="B176" s="6"/>
       <c r="C176" s="6"/>
@@ -3641,7 +4221,7 @@
       <c r="K176" s="6"/>
       <c r="L176" s="6"/>
     </row>
-    <row r="177" spans="1:12" ht="42.6" customHeight="1">
+    <row r="177" spans="1:12" ht="42.65" customHeight="1">
       <c r="A177" s="6"/>
       <c r="B177" s="6"/>
       <c r="C177" s="6"/>
@@ -3655,7 +4235,7 @@
       <c r="K177" s="6"/>
       <c r="L177" s="6"/>
     </row>
-    <row r="178" spans="1:12" ht="42.6" customHeight="1">
+    <row r="178" spans="1:12" ht="42.65" customHeight="1">
       <c r="A178" s="6"/>
       <c r="B178" s="6"/>
       <c r="C178" s="6"/>
@@ -3669,7 +4249,7 @@
       <c r="K178" s="6"/>
       <c r="L178" s="6"/>
     </row>
-    <row r="179" spans="1:12" ht="42.6" customHeight="1">
+    <row r="179" spans="1:12" ht="42.65" customHeight="1">
       <c r="A179" s="6"/>
       <c r="B179" s="6"/>
       <c r="C179" s="6"/>
@@ -3683,7 +4263,7 @@
       <c r="K179" s="6"/>
       <c r="L179" s="6"/>
     </row>
-    <row r="180" spans="1:12" ht="42.6" customHeight="1">
+    <row r="180" spans="1:12" ht="42.65" customHeight="1">
       <c r="A180" s="6"/>
       <c r="B180" s="6"/>
       <c r="C180" s="6"/>
@@ -3697,7 +4277,7 @@
       <c r="K180" s="6"/>
       <c r="L180" s="6"/>
     </row>
-    <row r="181" spans="1:12" ht="42.6" customHeight="1">
+    <row r="181" spans="1:12" ht="42.65" customHeight="1">
       <c r="A181" s="6"/>
       <c r="B181" s="6"/>
       <c r="C181" s="6"/>
@@ -3711,7 +4291,7 @@
       <c r="K181" s="6"/>
       <c r="L181" s="6"/>
     </row>
-    <row r="182" spans="1:12" ht="42.6" customHeight="1">
+    <row r="182" spans="1:12" ht="42.65" customHeight="1">
       <c r="A182" s="6"/>
       <c r="B182" s="6"/>
       <c r="C182" s="6"/>
@@ -3725,7 +4305,7 @@
       <c r="K182" s="6"/>
       <c r="L182" s="6"/>
     </row>
-    <row r="183" spans="1:12" ht="42.6" customHeight="1">
+    <row r="183" spans="1:12" ht="42.65" customHeight="1">
       <c r="A183" s="6"/>
       <c r="B183" s="6"/>
       <c r="C183" s="6"/>
@@ -3739,7 +4319,7 @@
       <c r="K183" s="6"/>
       <c r="L183" s="6"/>
     </row>
-    <row r="184" spans="1:12" ht="42.6" customHeight="1">
+    <row r="184" spans="1:12" ht="42.65" customHeight="1">
       <c r="A184" s="6"/>
       <c r="B184" s="6"/>
       <c r="C184" s="6"/>
@@ -3753,7 +4333,7 @@
       <c r="K184" s="6"/>
       <c r="L184" s="6"/>
     </row>
-    <row r="185" spans="1:12" ht="42.6" customHeight="1">
+    <row r="185" spans="1:12" ht="42.65" customHeight="1">
       <c r="A185" s="6"/>
       <c r="B185" s="6"/>
       <c r="C185" s="6"/>
@@ -3767,7 +4347,7 @@
       <c r="K185" s="6"/>
       <c r="L185" s="6"/>
     </row>
-    <row r="186" spans="1:12" ht="42.6" customHeight="1">
+    <row r="186" spans="1:12" ht="42.65" customHeight="1">
       <c r="A186" s="6"/>
       <c r="B186" s="6"/>
       <c r="C186" s="6"/>
@@ -3781,7 +4361,7 @@
       <c r="K186" s="6"/>
       <c r="L186" s="6"/>
     </row>
-    <row r="187" spans="1:12" ht="42.6" customHeight="1">
+    <row r="187" spans="1:12" ht="42.65" customHeight="1">
       <c r="A187" s="6"/>
       <c r="B187" s="6"/>
       <c r="C187" s="6"/>
@@ -3795,7 +4375,7 @@
       <c r="K187" s="6"/>
       <c r="L187" s="6"/>
     </row>
-    <row r="188" spans="1:12" ht="42.6" customHeight="1">
+    <row r="188" spans="1:12" ht="42.65" customHeight="1">
       <c r="A188" s="6"/>
       <c r="B188" s="6"/>
       <c r="C188" s="6"/>
@@ -3809,7 +4389,7 @@
       <c r="K188" s="6"/>
       <c r="L188" s="6"/>
     </row>
-    <row r="189" spans="1:12" ht="42.6" customHeight="1">
+    <row r="189" spans="1:12" ht="42.65" customHeight="1">
       <c r="A189" s="6"/>
       <c r="B189" s="6"/>
       <c r="C189" s="6"/>
@@ -3823,7 +4403,7 @@
       <c r="K189" s="6"/>
       <c r="L189" s="6"/>
     </row>
-    <row r="190" spans="1:12" ht="42.6" customHeight="1">
+    <row r="190" spans="1:12" ht="42.65" customHeight="1">
       <c r="A190" s="6"/>
       <c r="B190" s="6"/>
       <c r="C190" s="6"/>
@@ -3837,7 +4417,7 @@
       <c r="K190" s="6"/>
       <c r="L190" s="6"/>
     </row>
-    <row r="191" spans="1:12" ht="42.6" customHeight="1">
+    <row r="191" spans="1:12" ht="42.65" customHeight="1">
       <c r="A191" s="6"/>
       <c r="B191" s="6"/>
       <c r="C191" s="6"/>
@@ -3851,7 +4431,7 @@
       <c r="K191" s="6"/>
       <c r="L191" s="6"/>
     </row>
-    <row r="192" spans="1:12" ht="42.6" customHeight="1">
+    <row r="192" spans="1:12" ht="42.65" customHeight="1">
       <c r="A192" s="6"/>
       <c r="B192" s="6"/>
       <c r="C192" s="6"/>
@@ -3865,7 +4445,7 @@
       <c r="K192" s="6"/>
       <c r="L192" s="6"/>
     </row>
-    <row r="193" spans="1:12" ht="42.6" customHeight="1">
+    <row r="193" spans="1:12" ht="42.65" customHeight="1">
       <c r="A193" s="6"/>
       <c r="B193" s="6"/>
       <c r="C193" s="6"/>
@@ -3879,7 +4459,7 @@
       <c r="K193" s="6"/>
       <c r="L193" s="6"/>
     </row>
-    <row r="194" spans="1:12" ht="42.6" customHeight="1">
+    <row r="194" spans="1:12" ht="42.65" customHeight="1">
       <c r="A194" s="6"/>
       <c r="B194" s="6"/>
       <c r="C194" s="6"/>
@@ -3893,7 +4473,7 @@
       <c r="K194" s="6"/>
       <c r="L194" s="6"/>
     </row>
-    <row r="195" spans="1:12" ht="42.6" customHeight="1">
+    <row r="195" spans="1:12" ht="42.65" customHeight="1">
       <c r="A195" s="6"/>
       <c r="B195" s="6"/>
       <c r="C195" s="6"/>
@@ -3907,7 +4487,7 @@
       <c r="K195" s="6"/>
       <c r="L195" s="6"/>
     </row>
-    <row r="196" spans="1:12" ht="42.6" customHeight="1">
+    <row r="196" spans="1:12" ht="42.65" customHeight="1">
       <c r="A196" s="6"/>
       <c r="B196" s="6"/>
       <c r="C196" s="6"/>
@@ -3921,7 +4501,7 @@
       <c r="K196" s="6"/>
       <c r="L196" s="6"/>
     </row>
-    <row r="197" spans="1:12" ht="42.6" customHeight="1">
+    <row r="197" spans="1:12" ht="42.65" customHeight="1">
       <c r="A197" s="6"/>
       <c r="B197" s="6"/>
       <c r="C197" s="6"/>
@@ -3935,7 +4515,7 @@
       <c r="K197" s="6"/>
       <c r="L197" s="6"/>
     </row>
-    <row r="198" spans="1:12" ht="42.6" customHeight="1">
+    <row r="198" spans="1:12" ht="42.65" customHeight="1">
       <c r="A198" s="6"/>
       <c r="B198" s="6"/>
       <c r="C198" s="6"/>
@@ -3949,7 +4529,7 @@
       <c r="K198" s="6"/>
       <c r="L198" s="6"/>
     </row>
-    <row r="199" spans="1:12" ht="42.6" customHeight="1">
+    <row r="199" spans="1:12" ht="42.65" customHeight="1">
       <c r="A199" s="6"/>
       <c r="B199" s="6"/>
       <c r="C199" s="6"/>
@@ -3963,7 +4543,7 @@
       <c r="K199" s="6"/>
       <c r="L199" s="6"/>
     </row>
-    <row r="200" spans="1:12" ht="42.6" customHeight="1">
+    <row r="200" spans="1:12" ht="42.65" customHeight="1">
       <c r="A200" s="6"/>
       <c r="B200" s="6"/>
       <c r="C200" s="6"/>
@@ -4002,11 +4582,11 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
+    <dataValidation type="list" sqref="K8:K200" xr:uid="{00000000-0002-0000-0000-000001000000}">
+      <formula1>"未確認,修正済み,再テスト必要,対象外"</formula1>
+    </dataValidation>
     <dataValidation type="list" sqref="J8:J200" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"OK,不具合あり,未実施"</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="K8:K200" xr:uid="{00000000-0002-0000-0000-000001000000}">
-      <formula1>"未確認,修正済み,再テスト必要,対象外"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4019,21 +4599,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="62" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="21">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:6" ht="20">
+      <c r="A1" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
     </row>
     <row r="3" spans="1:6" ht="22.65" customHeight="1">
       <c r="A3" s="8" t="s">
@@ -4149,6 +4729,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100FFFAEB3A24D8254EA931476DB8D60440" ma:contentTypeVersion="9" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="c8d193e0f54e03b4175f5a4db63c885a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="d50c1a2a-6294-41b5-bbeb-a77cda6c64f4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e7e962f02e8fc9ae74e529f59a05e711" ns3:_="">
     <xsd:import namespace="d50c1a2a-6294-41b5-bbeb-a77cda6c64f4"/>
@@ -4324,15 +4913,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -4342,6 +4922,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55C5DA50-4866-466E-A4B2-AE8F0C9C1383}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9BB742F5-3D3F-4A88-B680-F1D8F2300B9A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4355,14 +4943,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55C5DA50-4866-466E-A4B2-AE8F0C9C1383}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/tests/tests.xlsx
+++ b/tests/tests.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nymgs\team04\tests\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moto\team04\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E19B21F1-69A9-4BFA-A405-B21F68656396}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{757BDCA9-A88B-4D04-933E-B38F5BB3AABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="テスト記録" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="148">
   <si>
     <t>ゲーム動作テスト記録</t>
   </si>
@@ -1012,6 +1012,111 @@
     <rPh sb="4" eb="6">
       <t>ハツドウ</t>
     </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>03-1</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>竹村茂杜</t>
+  </si>
+  <si>
+    <t>自機の移動・壁判定</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>ゲームを開始していること</t>
+  </si>
+  <si>
+    <t>方向キーで自機を上下左右に移動し、壁に向かって移動する。</t>
+  </si>
+  <si>
+    <t>自機が上下左右に移動し、壁をすり抜けない。</t>
+  </si>
+  <si>
+    <t>03-2</t>
+  </si>
+  <si>
+    <t>03-3</t>
+  </si>
+  <si>
+    <t>03-4</t>
+  </si>
+  <si>
+    <t>03-5</t>
+  </si>
+  <si>
+    <t>03-6</t>
+  </si>
+  <si>
+    <t>敵の追尾・巡回動作</t>
+  </si>
+  <si>
+    <t>NORMAL・HARDモードを開始していること</t>
+  </si>
+  <si>
+    <t>各難易度で敵の動きを確認する。</t>
+  </si>
+  <si>
+    <t>設定された敵が追尾・巡回・ランダム移動を正常に行う。</t>
+  </si>
+  <si>
+    <t>ゲームプレイ中であること</t>
+  </si>
+  <si>
+    <t>自機を敵に接触させる。</t>
+  </si>
+  <si>
+    <t>自機と敵の接触判定</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>バリア未所持時はゲームオーバー、バリア所持時はバリアを消費して攻撃を防ぐ。</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>NORMALモードの敵の動作</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>NORMALモードでゲームを開始していること</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>敵の動きを確認する。</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>追尾型と巡回・追尾型の敵が設定通りに動作する。</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>HARDモードの敵の動作</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>HARDモードでゲームを開始していること</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>ランダム型2体、追尾型1体、巡回・追尾型1体が設定通りに動作する。</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>敵の壁当たり判定</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>ゲームを開始していること</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>敵が壁や障害物に接触する様子を確認する。</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>敵が壁をすり抜けず、正常に移動する。</t>
     <phoneticPr fontId="6"/>
   </si>
 </sst>
@@ -1119,7 +1224,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1165,6 +1270,24 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="31" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1463,11 +1586,11 @@
     <row r="4" spans="1:12" ht="15.5">
       <c r="A4" s="2">
         <f>COUNTA(A8:A200)</f>
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B4" s="2">
         <f>COUNTIF(J8:J200,"OK")</f>
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C4" s="2">
         <f>COUNTIF(J8:J200,"不具合あり")</f>
@@ -1479,7 +1602,7 @@
       </c>
       <c r="E4" s="3">
         <f>IF(A4=0,0,B4/A4)</f>
-        <v>0.94444444444444442</v>
+        <v>0.95833333333333337</v>
       </c>
       <c r="F4" s="4">
         <v>45857.513194444444</v>
@@ -2108,86 +2231,194 @@
       <c r="L25" s="6"/>
     </row>
     <row r="26" spans="1:12" ht="42.65" customHeight="1">
-      <c r="A26" s="6"/>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="6"/>
+      <c r="A26" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="B26" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="D26" s="17">
+        <v>46225</v>
+      </c>
+      <c r="E26" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G26" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>44</v>
+      </c>
       <c r="I26" s="6"/>
-      <c r="J26" s="6"/>
+      <c r="J26" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="K26" s="6"/>
       <c r="L26" s="6"/>
     </row>
     <row r="27" spans="1:12" ht="42.65" customHeight="1">
-      <c r="A27" s="6"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
+      <c r="A27" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="D27" s="17">
+        <v>46225</v>
+      </c>
+      <c r="E27" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="F27" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="G27" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>44</v>
+      </c>
       <c r="I27" s="6"/>
-      <c r="J27" s="6"/>
+      <c r="J27" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="K27" s="6"/>
       <c r="L27" s="6"/>
     </row>
     <row r="28" spans="1:12" ht="42.65" customHeight="1">
-      <c r="A28" s="6"/>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
+      <c r="A28" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="B28" s="21" t="s">
+        <v>135</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="D28" s="17">
+        <v>46225</v>
+      </c>
+      <c r="E28" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="F28" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="G28" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>44</v>
+      </c>
       <c r="I28" s="6"/>
-      <c r="J28" s="6"/>
+      <c r="J28" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="K28" s="6"/>
       <c r="L28" s="6"/>
     </row>
     <row r="29" spans="1:12" ht="42.65" customHeight="1">
-      <c r="A29" s="6"/>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
+      <c r="A29" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="D29" s="17">
+        <v>46225</v>
+      </c>
+      <c r="E29" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="F29" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="G29" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>44</v>
+      </c>
       <c r="I29" s="6"/>
-      <c r="J29" s="6"/>
+      <c r="J29" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="K29" s="6"/>
       <c r="L29" s="6"/>
     </row>
     <row r="30" spans="1:12" ht="42.65" customHeight="1">
-      <c r="A30" s="6"/>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
+      <c r="A30" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="D30" s="17">
+        <v>46225</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="F30" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="G30" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>44</v>
+      </c>
       <c r="I30" s="6"/>
-      <c r="J30" s="6"/>
+      <c r="J30" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="K30" s="6"/>
       <c r="L30" s="6"/>
     </row>
     <row r="31" spans="1:12" ht="42.65" customHeight="1">
-      <c r="A31" s="6"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
+      <c r="A31" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B31" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="D31" s="17">
+        <v>46225</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>44</v>
+      </c>
       <c r="I31" s="6"/>
-      <c r="J31" s="6"/>
+      <c r="J31" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="K31" s="6"/>
       <c r="L31" s="6"/>
     </row>
@@ -4729,15 +4960,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100FFFAEB3A24D8254EA931476DB8D60440" ma:contentTypeVersion="9" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="c8d193e0f54e03b4175f5a4db63c885a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="d50c1a2a-6294-41b5-bbeb-a77cda6c64f4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e7e962f02e8fc9ae74e529f59a05e711" ns3:_="">
     <xsd:import namespace="d50c1a2a-6294-41b5-bbeb-a77cda6c64f4"/>
@@ -4913,6 +5135,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -4922,14 +5153,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55C5DA50-4866-466E-A4B2-AE8F0C9C1383}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9BB742F5-3D3F-4A88-B680-F1D8F2300B9A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4943,6 +5166,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55C5DA50-4866-466E-A4B2-AE8F0C9C1383}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
